--- a/research/traditional_assets/database/data/kenya/kenya_rubber_tires.xlsx
+++ b/research/traditional_assets/database/data/kenya/kenya_rubber_tires.xlsx
@@ -1266,7 +1266,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1403,22 +1403,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1683926490911662</v>
+        <v>0.1679189711438927</v>
       </c>
       <c r="C2">
-        <v>8.861668421031968</v>
+        <v>8.803879380397733</v>
       </c>
       <c r="D2">
-        <v>7.872668421031968</v>
+        <v>7.901579380397733</v>
       </c>
       <c r="E2">
-        <v>-3.45</v>
+        <v>-3.3633</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.0867</v>
       </c>
       <c r="G2">
         <v>0.989</v>
@@ -1439,28 +1439,28 @@
         <v>1.440408163265306</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.004361009999999999</v>
       </c>
       <c r="N2">
-        <v>1.440408163265306</v>
+        <v>1.436047153265306</v>
       </c>
       <c r="O2">
-        <v>0.4321224489795918</v>
+        <v>0.4308141459795918</v>
       </c>
       <c r="P2">
-        <v>1.008285714285714</v>
+        <v>1.005233007285714</v>
       </c>
       <c r="Q2">
-        <v>1.088285714285714</v>
+        <v>1.085233007285714</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1683926490911662</v>
+        <v>0.1692594658019118</v>
       </c>
       <c r="T2">
-        <v>0.8547702034345667</v>
+        <v>0.8608140331558212</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1477,7 +1477,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>330.2923321123561</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1485,22 +1485,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1679189711438927</v>
+        <v>0.1674452931966192</v>
       </c>
       <c r="C3">
-        <v>8.803879380397733</v>
+        <v>8.746303463021203</v>
       </c>
       <c r="D3">
-        <v>7.901579380397733</v>
+        <v>7.930703463021203</v>
       </c>
       <c r="E3">
-        <v>-3.3633</v>
+        <v>-3.2766</v>
       </c>
       <c r="F3">
-        <v>0.0867</v>
+        <v>0.1734</v>
       </c>
       <c r="G3">
         <v>0.989</v>
@@ -1521,28 +1521,28 @@
         <v>1.440408163265306</v>
       </c>
       <c r="M3">
-        <v>0.004361009999999999</v>
+        <v>0.008722019999999999</v>
       </c>
       <c r="N3">
-        <v>1.436047153265306</v>
+        <v>1.431686143265306</v>
       </c>
       <c r="O3">
-        <v>0.4308141459795918</v>
+        <v>0.4295058429795918</v>
       </c>
       <c r="P3">
-        <v>1.005233007285714</v>
+        <v>1.002180300285714</v>
       </c>
       <c r="Q3">
-        <v>1.085233007285714</v>
+        <v>1.082180300285714</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1692594658019118</v>
+        <v>0.1701439726496114</v>
       </c>
       <c r="T3">
-        <v>0.8608140331558212</v>
+        <v>0.8669812063407747</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1559,7 +1559,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>330.2923321123561</v>
+        <v>165.1461660561781</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1567,22 +1567,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1674452931966192</v>
+        <v>0.1669716152493457</v>
       </c>
       <c r="C4">
-        <v>8.746303463021203</v>
+        <v>8.688943034245517</v>
       </c>
       <c r="D4">
-        <v>7.930703463021203</v>
+        <v>7.960043034245516</v>
       </c>
       <c r="E4">
-        <v>-3.2766</v>
+        <v>-3.1899</v>
       </c>
       <c r="F4">
-        <v>0.1734</v>
+        <v>0.2601</v>
       </c>
       <c r="G4">
         <v>0.989</v>
@@ -1603,28 +1603,28 @@
         <v>1.440408163265306</v>
       </c>
       <c r="M4">
-        <v>0.008722019999999999</v>
+        <v>0.01308303</v>
       </c>
       <c r="N4">
-        <v>1.431686143265306</v>
+        <v>1.427325133265306</v>
       </c>
       <c r="O4">
-        <v>0.4295058429795918</v>
+        <v>0.4281975399795918</v>
       </c>
       <c r="P4">
-        <v>1.002180300285714</v>
+        <v>0.9991275932857142</v>
       </c>
       <c r="Q4">
-        <v>1.082180300285714</v>
+        <v>1.079127593285714</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1701439726496114</v>
+        <v>0.1710467167519028</v>
       </c>
       <c r="T4">
-        <v>0.8669812063407747</v>
+        <v>0.8732755377357273</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1641,7 +1641,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>165.1461660561781</v>
+        <v>110.097444037452</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1649,22 +1649,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1669716152493457</v>
+        <v>0.1664979373020722</v>
       </c>
       <c r="C5">
-        <v>8.688943034245517</v>
+        <v>8.631800494546047</v>
       </c>
       <c r="D5">
-        <v>7.960043034245516</v>
+        <v>7.989600494546046</v>
       </c>
       <c r="E5">
-        <v>-3.1899</v>
+        <v>-3.1032</v>
       </c>
       <c r="F5">
-        <v>0.2601</v>
+        <v>0.3468</v>
       </c>
       <c r="G5">
         <v>0.989</v>
@@ -1685,28 +1685,28 @@
         <v>1.440408163265306</v>
       </c>
       <c r="M5">
-        <v>0.01308303</v>
+        <v>0.01744404</v>
       </c>
       <c r="N5">
-        <v>1.427325133265306</v>
+        <v>1.422964123265306</v>
       </c>
       <c r="O5">
-        <v>0.4281975399795918</v>
+        <v>0.4268892369795918</v>
       </c>
       <c r="P5">
-        <v>0.9991275932857142</v>
+        <v>0.9960748862857143</v>
       </c>
       <c r="Q5">
-        <v>1.079127593285714</v>
+        <v>1.076074886285714</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1710467167519028</v>
+        <v>0.1719682680229919</v>
       </c>
       <c r="T5">
-        <v>0.8732755377357273</v>
+        <v>0.8797010010347415</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1723,7 +1723,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>110.097444037452</v>
+        <v>82.57308302808903</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1731,22 +1731,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1664979373020722</v>
+        <v>0.1660242593547987</v>
       </c>
       <c r="C6">
-        <v>8.631800494546047</v>
+        <v>8.574878280185116</v>
       </c>
       <c r="D6">
-        <v>7.989600494546046</v>
+        <v>8.019378280185116</v>
       </c>
       <c r="E6">
-        <v>-3.1032</v>
+        <v>-3.0165</v>
       </c>
       <c r="F6">
-        <v>0.3468</v>
+        <v>0.4335</v>
       </c>
       <c r="G6">
         <v>0.989</v>
@@ -1767,28 +1767,28 @@
         <v>1.440408163265306</v>
       </c>
       <c r="M6">
-        <v>0.01744404</v>
+        <v>0.02180505</v>
       </c>
       <c r="N6">
-        <v>1.422964123265306</v>
+        <v>1.418603113265306</v>
       </c>
       <c r="O6">
-        <v>0.4268892369795918</v>
+        <v>0.4255809339795918</v>
       </c>
       <c r="P6">
-        <v>0.9960748862857143</v>
+        <v>0.9930221792857143</v>
       </c>
       <c r="Q6">
-        <v>1.076074886285714</v>
+        <v>1.073022179285714</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1719682680229919</v>
+        <v>0.1729092203734723</v>
       </c>
       <c r="T6">
-        <v>0.8797010010347415</v>
+        <v>0.8862617372453138</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1805,7 +1805,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>82.57308302808903</v>
+        <v>66.05846642247123</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1813,22 +1813,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1660242593547987</v>
+        <v>0.1655505814075252</v>
       </c>
       <c r="C7">
-        <v>8.574878280185116</v>
+        <v>8.518178863881378</v>
       </c>
       <c r="D7">
-        <v>8.019378280185116</v>
+        <v>8.049378863881376</v>
       </c>
       <c r="E7">
-        <v>-3.0165</v>
+        <v>-2.9298</v>
       </c>
       <c r="F7">
-        <v>0.4335</v>
+        <v>0.5202</v>
       </c>
       <c r="G7">
         <v>0.989</v>
@@ -1849,28 +1849,28 @@
         <v>1.440408163265306</v>
       </c>
       <c r="M7">
-        <v>0.02180505</v>
+        <v>0.02616606</v>
       </c>
       <c r="N7">
-        <v>1.418603113265306</v>
+        <v>1.414242103265306</v>
       </c>
       <c r="O7">
-        <v>0.4255809339795918</v>
+        <v>0.4242726309795918</v>
       </c>
       <c r="P7">
-        <v>0.9930221792857143</v>
+        <v>0.9899694722857142</v>
       </c>
       <c r="Q7">
-        <v>1.073022179285714</v>
+        <v>1.069969472285714</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1729092203734723</v>
+        <v>0.173870192986729</v>
       </c>
       <c r="T7">
-        <v>0.8862617372453138</v>
+        <v>0.892962063588026</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1887,7 +1887,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>66.05846642247123</v>
+        <v>55.04872201872602</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1895,22 +1895,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1655505814075252</v>
+        <v>0.1650769034602517</v>
       </c>
       <c r="C8">
-        <v>8.518178863881378</v>
+        <v>8.461704755494299</v>
       </c>
       <c r="D8">
-        <v>8.049378863881376</v>
+        <v>8.079604755494298</v>
       </c>
       <c r="E8">
-        <v>-2.9298</v>
+        <v>-2.8431</v>
       </c>
       <c r="F8">
-        <v>0.5202</v>
+        <v>0.6068999999999999</v>
       </c>
       <c r="G8">
         <v>0.989</v>
@@ -1931,28 +1931,28 @@
         <v>1.440408163265306</v>
       </c>
       <c r="M8">
-        <v>0.02616606</v>
+        <v>0.03052706999999999</v>
       </c>
       <c r="N8">
-        <v>1.414242103265306</v>
+        <v>1.409881093265306</v>
       </c>
       <c r="O8">
-        <v>0.4242726309795918</v>
+        <v>0.4229643279795918</v>
       </c>
       <c r="P8">
-        <v>0.9899694722857142</v>
+        <v>0.9869167652857143</v>
       </c>
       <c r="Q8">
-        <v>1.069969472285714</v>
+        <v>1.066916765285714</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.173870192986729</v>
+        <v>0.17485183167769</v>
       </c>
       <c r="T8">
-        <v>0.892962063588026</v>
+        <v>0.8998064829703665</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1969,7 +1969,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>55.04872201872602</v>
+        <v>47.18461887319374</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1977,22 +1977,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1650769034602517</v>
+        <v>0.1646032255129783</v>
       </c>
       <c r="C9">
-        <v>8.461704755494299</v>
+        <v>8.40545850272413</v>
       </c>
       <c r="D9">
-        <v>8.079604755494298</v>
+        <v>8.110058502724129</v>
       </c>
       <c r="E9">
-        <v>-2.8431</v>
+        <v>-2.7564</v>
       </c>
       <c r="F9">
-        <v>0.6069000000000001</v>
+        <v>0.6936</v>
       </c>
       <c r="G9">
         <v>0.989</v>
@@ -2013,28 +2013,28 @@
         <v>1.440408163265306</v>
       </c>
       <c r="M9">
-        <v>0.03052707</v>
+        <v>0.03488807999999999</v>
       </c>
       <c r="N9">
-        <v>1.409881093265306</v>
+        <v>1.405520083265306</v>
       </c>
       <c r="O9">
-        <v>0.4229643279795918</v>
+        <v>0.4216560249795918</v>
       </c>
       <c r="P9">
-        <v>0.9869167652857143</v>
+        <v>0.9838640582857143</v>
       </c>
       <c r="Q9">
-        <v>1.066916765285714</v>
+        <v>1.063864058285714</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.17485183167769</v>
+        <v>0.1758548103401937</v>
       </c>
       <c r="T9">
-        <v>0.8998064829703665</v>
+        <v>0.9067996940784099</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2051,7 +2051,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>47.18461887319372</v>
+        <v>41.28654151404452</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2059,22 +2059,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1646032255129783</v>
+        <v>0.1641295475657047</v>
       </c>
       <c r="C10">
-        <v>8.40545850272413</v>
+        <v>8.349442691827745</v>
       </c>
       <c r="D10">
-        <v>8.110058502724129</v>
+        <v>8.140742691827745</v>
       </c>
       <c r="E10">
-        <v>-2.7564</v>
+        <v>-2.6697</v>
       </c>
       <c r="F10">
-        <v>0.6936</v>
+        <v>0.7803</v>
       </c>
       <c r="G10">
         <v>0.989</v>
@@ -2095,28 +2095,28 @@
         <v>1.440408163265306</v>
       </c>
       <c r="M10">
-        <v>0.03488807999999999</v>
+        <v>0.03924909</v>
       </c>
       <c r="N10">
-        <v>1.405520083265306</v>
+        <v>1.401159073265306</v>
       </c>
       <c r="O10">
-        <v>0.4216560249795918</v>
+        <v>0.4203477219795918</v>
       </c>
       <c r="P10">
-        <v>0.9838640582857143</v>
+        <v>0.9808113512857143</v>
       </c>
       <c r="Q10">
-        <v>1.063864058285714</v>
+        <v>1.060811351285714</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1758548103401937</v>
+        <v>0.1768798324897854</v>
       </c>
       <c r="T10">
-        <v>0.9067996940784099</v>
+        <v>0.9139466021338828</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2133,7 +2133,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>41.28654151404452</v>
+        <v>36.69914801248401</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2141,22 +2141,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1641295475657047</v>
+        <v>0.1636558696184312</v>
       </c>
       <c r="C11">
-        <v>8.349442691827745</v>
+        <v>8.293659948350788</v>
       </c>
       <c r="D11">
-        <v>8.140742691827745</v>
+        <v>8.171659948350786</v>
       </c>
       <c r="E11">
-        <v>-2.6697</v>
+        <v>-2.583</v>
       </c>
       <c r="F11">
-        <v>0.7803</v>
+        <v>0.8669999999999999</v>
       </c>
       <c r="G11">
         <v>0.989</v>
@@ -2177,28 +2177,28 @@
         <v>1.440408163265306</v>
       </c>
       <c r="M11">
-        <v>0.03924909</v>
+        <v>0.04361009999999999</v>
       </c>
       <c r="N11">
-        <v>1.401159073265306</v>
+        <v>1.396798063265306</v>
       </c>
       <c r="O11">
-        <v>0.4203477219795918</v>
+        <v>0.4190394189795918</v>
       </c>
       <c r="P11">
-        <v>0.9808113512857143</v>
+        <v>0.9777586442857142</v>
       </c>
       <c r="Q11">
-        <v>1.060811351285714</v>
+        <v>1.057758644285714</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1768798324897854</v>
+        <v>0.177927632909368</v>
       </c>
       <c r="T11">
-        <v>0.9139466021338828</v>
+        <v>0.9212523303683663</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2215,7 +2215,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>36.69914801248401</v>
+        <v>33.02923321123561</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2223,22 +2223,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1636558696184312</v>
+        <v>0.1631821916711577</v>
       </c>
       <c r="C12">
-        <v>8.293659948350786</v>
+        <v>8.238112937876606</v>
       </c>
       <c r="D12">
-        <v>8.171659948350786</v>
+        <v>8.202812937876605</v>
       </c>
       <c r="E12">
-        <v>-2.583</v>
+        <v>-2.4963</v>
       </c>
       <c r="F12">
-        <v>0.867</v>
+        <v>0.9537</v>
       </c>
       <c r="G12">
         <v>0.989</v>
@@ -2259,28 +2259,28 @@
         <v>1.440408163265306</v>
       </c>
       <c r="M12">
-        <v>0.0436101</v>
+        <v>0.04797111</v>
       </c>
       <c r="N12">
-        <v>1.396798063265306</v>
+        <v>1.392437053265306</v>
       </c>
       <c r="O12">
-        <v>0.4190394189795918</v>
+        <v>0.4177311159795918</v>
       </c>
       <c r="P12">
-        <v>0.9777586442857142</v>
+        <v>0.9747059372857143</v>
       </c>
       <c r="Q12">
-        <v>1.057758644285714</v>
+        <v>1.054705937285714</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.177927632909368</v>
+        <v>0.1789989794057952</v>
       </c>
       <c r="T12">
-        <v>0.9212523303683663</v>
+        <v>0.9287222322710403</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2297,7 +2297,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>33.02923321123561</v>
+        <v>30.02657564657783</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2305,22 +2305,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1631821916711577</v>
+        <v>0.1627085137238843</v>
       </c>
       <c r="C13">
-        <v>8.238112937876606</v>
+        <v>8.182804366792324</v>
       </c>
       <c r="D13">
-        <v>8.202812937876605</v>
+        <v>8.234204366792323</v>
       </c>
       <c r="E13">
-        <v>-2.4963</v>
+        <v>-2.4096</v>
       </c>
       <c r="F13">
-        <v>0.9537</v>
+        <v>1.0404</v>
       </c>
       <c r="G13">
         <v>0.989</v>
@@ -2341,28 +2341,28 @@
         <v>1.440408163265306</v>
       </c>
       <c r="M13">
-        <v>0.04797111</v>
+        <v>0.05233212</v>
       </c>
       <c r="N13">
-        <v>1.392437053265306</v>
+        <v>1.388076043265306</v>
       </c>
       <c r="O13">
-        <v>0.4177311159795918</v>
+        <v>0.4164228129795918</v>
       </c>
       <c r="P13">
-        <v>0.9747059372857143</v>
+        <v>0.9716532302857143</v>
       </c>
       <c r="Q13">
-        <v>1.054705937285714</v>
+        <v>1.051653230285714</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1789989794057952</v>
+        <v>0.1800946746862321</v>
       </c>
       <c r="T13">
-        <v>0.9287222322710403</v>
+        <v>0.9363619046715026</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2379,7 +2379,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>30.02657564657783</v>
+        <v>27.52436100936301</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2387,22 +2387,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1627085137238843</v>
+        <v>0.1622348357766107</v>
       </c>
       <c r="C14">
-        <v>8.182804366792324</v>
+        <v>8.127736983072644</v>
       </c>
       <c r="D14">
-        <v>8.234204366792323</v>
+        <v>8.265836983072644</v>
       </c>
       <c r="E14">
-        <v>-2.4096</v>
+        <v>-2.3229</v>
       </c>
       <c r="F14">
-        <v>1.0404</v>
+        <v>1.1271</v>
       </c>
       <c r="G14">
         <v>0.989</v>
@@ -2423,28 +2423,28 @@
         <v>1.440408163265306</v>
       </c>
       <c r="M14">
-        <v>0.05233212</v>
+        <v>0.05669312999999999</v>
       </c>
       <c r="N14">
-        <v>1.388076043265306</v>
+        <v>1.383715033265306</v>
       </c>
       <c r="O14">
-        <v>0.4164228129795918</v>
+        <v>0.4151145099795918</v>
       </c>
       <c r="P14">
-        <v>0.9716532302857143</v>
+        <v>0.9686005232857142</v>
       </c>
       <c r="Q14">
-        <v>1.051653230285714</v>
+        <v>1.048600523285714</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1800946746862321</v>
+        <v>0.1812155583639204</v>
       </c>
       <c r="T14">
-        <v>0.9363619046715026</v>
+        <v>0.9441772017248489</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2461,7 +2461,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>27.52436100936301</v>
+        <v>25.40710247018124</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2469,22 +2469,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1622348357766107</v>
+        <v>0.1617611578293372</v>
       </c>
       <c r="C15">
-        <v>8.127736983072644</v>
+        <v>8.072913577081696</v>
       </c>
       <c r="D15">
-        <v>8.265836983072644</v>
+        <v>8.297713577081696</v>
       </c>
       <c r="E15">
-        <v>-2.3229</v>
+        <v>-2.2362</v>
       </c>
       <c r="F15">
-        <v>1.1271</v>
+        <v>1.2138</v>
       </c>
       <c r="G15">
         <v>0.989</v>
@@ -2505,28 +2505,28 @@
         <v>1.440408163265306</v>
       </c>
       <c r="M15">
-        <v>0.05669312999999999</v>
+        <v>0.06105414000000001</v>
       </c>
       <c r="N15">
-        <v>1.383715033265306</v>
+        <v>1.379354023265306</v>
       </c>
       <c r="O15">
-        <v>0.4151145099795918</v>
+        <v>0.4138062069795918</v>
       </c>
       <c r="P15">
-        <v>0.9686005232857142</v>
+        <v>0.9655478162857143</v>
       </c>
       <c r="Q15">
-        <v>1.048600523285714</v>
+        <v>1.045547816285714</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1812155583639204</v>
+        <v>0.1823625091038805</v>
       </c>
       <c r="T15">
-        <v>0.9441772017248489</v>
+        <v>0.9521742498724591</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2543,7 +2543,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>25.40710247018124</v>
+        <v>23.59230943659686</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2551,22 +2551,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1617611578293372</v>
+        <v>0.1612874798820637</v>
       </c>
       <c r="C16">
-        <v>8.072913577081696</v>
+        <v>8.018336982393599</v>
       </c>
       <c r="D16">
-        <v>8.297713577081696</v>
+        <v>8.329836982393598</v>
       </c>
       <c r="E16">
-        <v>-2.2362</v>
+        <v>-2.1495</v>
       </c>
       <c r="F16">
-        <v>1.2138</v>
+        <v>1.3005</v>
       </c>
       <c r="G16">
         <v>0.989</v>
@@ -2587,28 +2587,28 @@
         <v>1.440408163265306</v>
       </c>
       <c r="M16">
-        <v>0.06105414000000001</v>
+        <v>0.06541515000000001</v>
       </c>
       <c r="N16">
-        <v>1.379354023265306</v>
+        <v>1.374993013265306</v>
       </c>
       <c r="O16">
-        <v>0.4138062069795918</v>
+        <v>0.4124979039795918</v>
       </c>
       <c r="P16">
-        <v>0.9655478162857143</v>
+        <v>0.9624951092857144</v>
       </c>
       <c r="Q16">
-        <v>1.045547816285714</v>
+        <v>1.042495109285714</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1823625091038805</v>
+        <v>0.183536446920075</v>
       </c>
       <c r="T16">
-        <v>0.9521742498724591</v>
+        <v>0.9603594638588366</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2625,7 +2625,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>23.59230943659686</v>
+        <v>22.0194888074904</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2633,22 +2633,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1612874798820637</v>
+        <v>0.1608138019347902</v>
       </c>
       <c r="C17">
-        <v>8.018336982393599</v>
+        <v>7.964010076632094</v>
       </c>
       <c r="D17">
-        <v>8.329836982393598</v>
+        <v>8.362210076632094</v>
       </c>
       <c r="E17">
-        <v>-2.1495</v>
+        <v>-2.0628</v>
       </c>
       <c r="F17">
-        <v>1.3005</v>
+        <v>1.3872</v>
       </c>
       <c r="G17">
         <v>0.989</v>
@@ -2669,28 +2669,28 @@
         <v>1.440408163265306</v>
       </c>
       <c r="M17">
-        <v>0.06541514999999999</v>
+        <v>0.06977615999999999</v>
       </c>
       <c r="N17">
-        <v>1.374993013265306</v>
+        <v>1.370632003265306</v>
       </c>
       <c r="O17">
-        <v>0.4124979039795918</v>
+        <v>0.4111896009795918</v>
       </c>
       <c r="P17">
-        <v>0.9624951092857144</v>
+        <v>0.9594424022857142</v>
       </c>
       <c r="Q17">
-        <v>1.042495109285714</v>
+        <v>1.039442402285714</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.183536446920075</v>
+        <v>0.184738335636655</v>
       </c>
       <c r="T17">
-        <v>0.9603594638588366</v>
+        <v>0.9687395638925088</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2707,7 +2707,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>22.01948880749041</v>
+        <v>20.64327075702226</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2715,22 +2715,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1608138019347902</v>
+        <v>0.1603401239875167</v>
       </c>
       <c r="C18">
-        <v>7.964010076632094</v>
+        <v>7.909935782329876</v>
       </c>
       <c r="D18">
-        <v>8.362210076632094</v>
+        <v>8.394835782329876</v>
       </c>
       <c r="E18">
-        <v>-2.0628</v>
+        <v>-1.9761</v>
       </c>
       <c r="F18">
-        <v>1.3872</v>
+        <v>1.4739</v>
       </c>
       <c r="G18">
         <v>0.989</v>
@@ -2751,28 +2751,28 @@
         <v>1.440408163265306</v>
       </c>
       <c r="M18">
-        <v>0.06977615999999999</v>
+        <v>0.07413717</v>
       </c>
       <c r="N18">
-        <v>1.370632003265306</v>
+        <v>1.366270993265306</v>
       </c>
       <c r="O18">
-        <v>0.4111896009795918</v>
+        <v>0.4098812979795918</v>
       </c>
       <c r="P18">
-        <v>0.9594424022857142</v>
+        <v>0.9563896952857143</v>
       </c>
       <c r="Q18">
-        <v>1.039442402285714</v>
+        <v>1.036389695285714</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.184738335636655</v>
+        <v>0.1859691855271286</v>
       </c>
       <c r="T18">
-        <v>0.9687395638925088</v>
+        <v>0.9773215940474745</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2789,7 +2789,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>20.64327075702226</v>
+        <v>19.42896071249153</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2797,22 +2797,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1603401239875167</v>
+        <v>0.1598664460402432</v>
       </c>
       <c r="C19">
-        <v>7.909935782329876</v>
+        <v>7.856117067808085</v>
       </c>
       <c r="D19">
-        <v>8.394835782329876</v>
+        <v>8.427717067808084</v>
       </c>
       <c r="E19">
-        <v>-1.9761</v>
+        <v>-1.8894</v>
       </c>
       <c r="F19">
-        <v>1.4739</v>
+        <v>1.5606</v>
       </c>
       <c r="G19">
         <v>0.989</v>
@@ -2833,28 +2833,28 @@
         <v>1.440408163265306</v>
       </c>
       <c r="M19">
-        <v>0.07413717</v>
+        <v>0.07849818</v>
       </c>
       <c r="N19">
-        <v>1.366270993265306</v>
+        <v>1.361909983265306</v>
       </c>
       <c r="O19">
-        <v>0.4098812979795918</v>
+        <v>0.4085729949795918</v>
       </c>
       <c r="P19">
-        <v>0.9563896952857143</v>
+        <v>0.9533369882857143</v>
       </c>
       <c r="Q19">
-        <v>1.036389695285714</v>
+        <v>1.033336988285714</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1859691855271286</v>
+        <v>0.1872300561466381</v>
       </c>
       <c r="T19">
-        <v>0.9773215940474745</v>
+        <v>0.9861129420110976</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2871,7 +2871,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>19.42896071249153</v>
+        <v>18.349574006242</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2879,22 +2879,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1598664460402432</v>
+        <v>0.1593927680929697</v>
       </c>
       <c r="C20">
-        <v>7.856117067808085</v>
+        <v>7.802556948076566</v>
       </c>
       <c r="D20">
-        <v>8.427717067808084</v>
+        <v>8.460856948076565</v>
       </c>
       <c r="E20">
-        <v>-1.8894</v>
+        <v>-1.8027</v>
       </c>
       <c r="F20">
-        <v>1.5606</v>
+        <v>1.6473</v>
       </c>
       <c r="G20">
         <v>0.989</v>
@@ -2915,28 +2915,28 @@
         <v>1.440408163265306</v>
       </c>
       <c r="M20">
-        <v>0.07849818</v>
+        <v>0.08285919</v>
       </c>
       <c r="N20">
-        <v>1.361909983265306</v>
+        <v>1.357548973265306</v>
       </c>
       <c r="O20">
-        <v>0.4085729949795918</v>
+        <v>0.4072646919795918</v>
       </c>
       <c r="P20">
-        <v>0.9533369882857143</v>
+        <v>0.9502842812857143</v>
       </c>
       <c r="Q20">
-        <v>1.033336988285714</v>
+        <v>1.030284281285714</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1872300561466381</v>
+        <v>0.1885220593740367</v>
       </c>
       <c r="T20">
-        <v>0.9861129420110976</v>
+        <v>0.9951213602948102</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -2953,7 +2953,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>18.349574006242</v>
+        <v>17.3838069532819</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2961,22 +2961,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1593927680929697</v>
+        <v>0.1589190901456962</v>
       </c>
       <c r="C21">
-        <v>7.802556948076566</v>
+        <v>7.749258485755462</v>
       </c>
       <c r="D21">
-        <v>8.460856948076565</v>
+        <v>8.494258485755461</v>
       </c>
       <c r="E21">
-        <v>-1.8027</v>
+        <v>-1.716</v>
       </c>
       <c r="F21">
-        <v>1.6473</v>
+        <v>1.734</v>
       </c>
       <c r="G21">
         <v>0.989</v>
@@ -2997,28 +2997,28 @@
         <v>1.440408163265306</v>
       </c>
       <c r="M21">
-        <v>0.08285919</v>
+        <v>0.0872202</v>
       </c>
       <c r="N21">
-        <v>1.357548973265306</v>
+        <v>1.353187963265306</v>
       </c>
       <c r="O21">
-        <v>0.4072646919795918</v>
+        <v>0.4059563889795918</v>
       </c>
       <c r="P21">
-        <v>0.9502842812857143</v>
+        <v>0.9472315742857143</v>
       </c>
       <c r="Q21">
-        <v>1.030284281285714</v>
+        <v>1.027231574285714</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1885220593740367</v>
+        <v>0.1898463626821203</v>
       </c>
       <c r="T21">
-        <v>0.9951213602948102</v>
+        <v>1.004354989035616</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3035,7 +3035,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>17.3838069532819</v>
+        <v>16.5146166056178</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3043,22 +3043,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1589190901456962</v>
+        <v>0.1584454121984227</v>
       </c>
       <c r="C22">
-        <v>7.749258485755462</v>
+        <v>7.6962247920187</v>
       </c>
       <c r="D22">
-        <v>8.494258485755461</v>
+        <v>8.5279247920187</v>
       </c>
       <c r="E22">
-        <v>-1.716</v>
+        <v>-1.6293</v>
       </c>
       <c r="F22">
-        <v>1.734</v>
+        <v>1.8207</v>
       </c>
       <c r="G22">
         <v>0.989</v>
@@ -3079,28 +3079,28 @@
         <v>1.440408163265306</v>
       </c>
       <c r="M22">
-        <v>0.0872202</v>
+        <v>0.09158121000000001</v>
       </c>
       <c r="N22">
-        <v>1.353187963265306</v>
+        <v>1.348826953265306</v>
       </c>
       <c r="O22">
-        <v>0.4059563889795918</v>
+        <v>0.4046480859795918</v>
       </c>
       <c r="P22">
-        <v>0.9472315742857143</v>
+        <v>0.9441788672857143</v>
       </c>
       <c r="Q22">
-        <v>1.027231574285714</v>
+        <v>1.024178867285714</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1898463626821203</v>
+        <v>0.1912041926562313</v>
       </c>
       <c r="T22">
-        <v>1.004354989035616</v>
+        <v>1.013822380529353</v>
       </c>
       <c r="U22">
         <v>0.0503</v>
@@ -3117,7 +3117,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>16.5146166056178</v>
+        <v>15.72820629106458</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3125,22 +3125,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1584454121984227</v>
+        <v>0.1579717342511492</v>
       </c>
       <c r="C23">
-        <v>7.696224792018704</v>
+        <v>7.643459027560024</v>
       </c>
       <c r="D23">
-        <v>8.527924792018704</v>
+        <v>8.561859027560024</v>
       </c>
       <c r="E23">
-        <v>-1.6293</v>
+        <v>-1.5426</v>
       </c>
       <c r="F23">
-        <v>1.8207</v>
+        <v>1.9074</v>
       </c>
       <c r="G23">
         <v>0.989</v>
@@ -3161,28 +3161,28 @@
         <v>1.440408163265306</v>
       </c>
       <c r="M23">
-        <v>0.09158121</v>
+        <v>0.09594221999999999</v>
       </c>
       <c r="N23">
-        <v>1.348826953265306</v>
+        <v>1.344465943265306</v>
       </c>
       <c r="O23">
-        <v>0.4046480859795918</v>
+        <v>0.4033397829795918</v>
       </c>
       <c r="P23">
-        <v>0.9441788672857143</v>
+        <v>0.9411261602857143</v>
       </c>
       <c r="Q23">
-        <v>1.024178867285714</v>
+        <v>1.021126160285714</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1912041926562313</v>
+        <v>0.1925968387835247</v>
       </c>
       <c r="T23">
-        <v>1.013822380529353</v>
+        <v>1.023532525651135</v>
       </c>
       <c r="U23">
         <v>0.0503</v>
@@ -3199,7 +3199,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>15.72820629106458</v>
+        <v>15.01328782328891</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3207,22 +3207,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1579717342511492</v>
+        <v>0.1574980563038757</v>
       </c>
       <c r="C24">
-        <v>7.643459027560024</v>
+        <v>7.59096440358217</v>
       </c>
       <c r="D24">
-        <v>8.561859027560024</v>
+        <v>8.596064403582169</v>
       </c>
       <c r="E24">
-        <v>-1.5426</v>
+        <v>-1.4559</v>
       </c>
       <c r="F24">
-        <v>1.9074</v>
+        <v>1.9941</v>
       </c>
       <c r="G24">
         <v>0.989</v>
@@ -3243,28 +3243,28 @@
         <v>1.440408163265306</v>
       </c>
       <c r="M24">
-        <v>0.09594221999999999</v>
+        <v>0.10030323</v>
       </c>
       <c r="N24">
-        <v>1.344465943265306</v>
+        <v>1.340104933265306</v>
       </c>
       <c r="O24">
-        <v>0.4033397829795918</v>
+        <v>0.4020314799795918</v>
       </c>
       <c r="P24">
-        <v>0.9411261602857143</v>
+        <v>0.9380734532857142</v>
       </c>
       <c r="Q24">
-        <v>1.021126160285714</v>
+        <v>1.018073453285714</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1925968387835247</v>
+        <v>0.194025657537501</v>
       </c>
       <c r="T24">
-        <v>1.023532525651135</v>
+        <v>1.033494882334521</v>
       </c>
       <c r="U24">
         <v>0.0503</v>
@@ -3281,7 +3281,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>15.01328782328891</v>
+        <v>14.36053617879809</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3289,22 +3289,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1574980563038757</v>
+        <v>0.1570243783566022</v>
       </c>
       <c r="C25">
-        <v>7.59096440358217</v>
+        <v>7.538744182809843</v>
       </c>
       <c r="D25">
-        <v>8.596064403582169</v>
+        <v>8.630544182809842</v>
       </c>
       <c r="E25">
-        <v>-1.4559</v>
+        <v>-1.3692</v>
       </c>
       <c r="F25">
-        <v>1.9941</v>
+        <v>2.0808</v>
       </c>
       <c r="G25">
         <v>0.989</v>
@@ -3325,28 +3325,28 @@
         <v>1.440408163265306</v>
       </c>
       <c r="M25">
-        <v>0.10030323</v>
+        <v>0.10466424</v>
       </c>
       <c r="N25">
-        <v>1.340104933265306</v>
+        <v>1.335743923265306</v>
       </c>
       <c r="O25">
-        <v>0.4020314799795918</v>
+        <v>0.4007231769795918</v>
       </c>
       <c r="P25">
-        <v>0.9380734532857142</v>
+        <v>0.9350207462857143</v>
       </c>
       <c r="Q25">
-        <v>1.018073453285714</v>
+        <v>1.015020746285714</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.194025657537501</v>
+        <v>0.1954920767850029</v>
       </c>
       <c r="T25">
-        <v>1.033494882334521</v>
+        <v>1.04371940629905</v>
       </c>
       <c r="U25">
         <v>0.0503</v>
@@ -3363,7 +3363,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>14.36053617879809</v>
+        <v>13.76218050468151</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3371,22 +3371,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1570243783566022</v>
+        <v>0.1565507004093288</v>
       </c>
       <c r="C26">
-        <v>7.538744182809843</v>
+        <v>7.486801680527197</v>
       </c>
       <c r="D26">
-        <v>8.630544182809842</v>
+        <v>8.665301680527197</v>
       </c>
       <c r="E26">
-        <v>-1.3692</v>
+        <v>-1.2825</v>
       </c>
       <c r="F26">
-        <v>2.0808</v>
+        <v>2.1675</v>
       </c>
       <c r="G26">
         <v>0.989</v>
@@ -3407,28 +3407,28 @@
         <v>1.440408163265306</v>
       </c>
       <c r="M26">
-        <v>0.10466424</v>
+        <v>0.10902525</v>
       </c>
       <c r="N26">
-        <v>1.335743923265306</v>
+        <v>1.331382913265306</v>
       </c>
       <c r="O26">
-        <v>0.4007231769795918</v>
+        <v>0.3994148739795918</v>
       </c>
       <c r="P26">
-        <v>0.9350207462857143</v>
+        <v>0.9319680392857144</v>
       </c>
       <c r="Q26">
-        <v>1.015020746285714</v>
+        <v>1.011968039285714</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1954920767850029</v>
+        <v>0.1969976005457717</v>
       </c>
       <c r="T26">
-        <v>1.04371940629905</v>
+        <v>1.054216584235966</v>
       </c>
       <c r="U26">
         <v>0.0503</v>
@@ -3445,7 +3445,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>13.76218050468151</v>
+        <v>13.21169328449425</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3453,22 +3453,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1565507004093288</v>
+        <v>0.1563500224620553</v>
       </c>
       <c r="C27">
-        <v>7.486801680527197</v>
+        <v>7.414911580136596</v>
       </c>
       <c r="D27">
-        <v>8.665301680527197</v>
+        <v>8.680111580136595</v>
       </c>
       <c r="E27">
-        <v>-1.2825</v>
+        <v>-1.1958</v>
       </c>
       <c r="F27">
-        <v>2.1675</v>
+        <v>2.2542</v>
       </c>
       <c r="G27">
         <v>0.989</v>
@@ -3489,45 +3489,45 @@
         <v>1.440408163265306</v>
       </c>
       <c r="M27">
-        <v>0.10902525</v>
+        <v>0.11676756</v>
       </c>
       <c r="N27">
-        <v>1.331382913265306</v>
+        <v>1.323640603265306</v>
       </c>
       <c r="O27">
-        <v>0.3994148739795918</v>
+        <v>0.3970921809795918</v>
       </c>
       <c r="P27">
-        <v>0.9319680392857144</v>
+        <v>0.9265484222857143</v>
       </c>
       <c r="Q27">
-        <v>1.011968039285714</v>
+        <v>1.006548422285714</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1969976005457717</v>
+        <v>0.1985438141379125</v>
       </c>
       <c r="T27">
-        <v>1.054216584235966</v>
+        <v>1.06499746968469</v>
       </c>
       <c r="U27">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V27">
         <v>0.3</v>
       </c>
       <c r="W27">
-        <v>0.03521</v>
+        <v>0.03625999999999999</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y27">
-        <v>13.21169328449425</v>
+        <v>12.33568778233703</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3535,22 +3535,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1563500224620553</v>
+        <v>0.1558868445147817</v>
       </c>
       <c r="C28">
-        <v>7.414911580136596</v>
+        <v>7.362587831708701</v>
       </c>
       <c r="D28">
-        <v>8.680111580136595</v>
+        <v>8.7144878317087</v>
       </c>
       <c r="E28">
-        <v>-1.1958</v>
+        <v>-1.1091</v>
       </c>
       <c r="F28">
-        <v>2.2542</v>
+        <v>2.3409</v>
       </c>
       <c r="G28">
         <v>0.989</v>
@@ -3571,28 +3571,28 @@
         <v>1.440408163265306</v>
       </c>
       <c r="M28">
-        <v>0.11676756</v>
+        <v>0.12125862</v>
       </c>
       <c r="N28">
-        <v>1.323640603265306</v>
+        <v>1.319149543265306</v>
       </c>
       <c r="O28">
-        <v>0.3970921809795918</v>
+        <v>0.3957448629795918</v>
       </c>
       <c r="P28">
-        <v>0.9265484222857143</v>
+        <v>0.9234046802857142</v>
       </c>
       <c r="Q28">
-        <v>1.006548422285714</v>
+        <v>1.003404680285714</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1985438141379125</v>
+        <v>0.2001323897462764</v>
       </c>
       <c r="T28">
-        <v>1.06499746968469</v>
+        <v>1.076073721858037</v>
       </c>
       <c r="U28">
         <v>0.0518</v>
@@ -3609,7 +3609,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>12.33568778233703</v>
+        <v>11.87881045706529</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3617,22 +3617,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1558868445147817</v>
+        <v>0.1554236665675082</v>
       </c>
       <c r="C29">
-        <v>7.362587831708701</v>
+        <v>7.310537449657923</v>
       </c>
       <c r="D29">
-        <v>8.7144878317087</v>
+        <v>8.749137449657923</v>
       </c>
       <c r="E29">
-        <v>-1.1091</v>
+        <v>-1.0224</v>
       </c>
       <c r="F29">
-        <v>2.3409</v>
+        <v>2.4276</v>
       </c>
       <c r="G29">
         <v>0.989</v>
@@ -3653,28 +3653,28 @@
         <v>1.440408163265306</v>
       </c>
       <c r="M29">
-        <v>0.12125862</v>
+        <v>0.12574968</v>
       </c>
       <c r="N29">
-        <v>1.319149543265306</v>
+        <v>1.314658483265306</v>
       </c>
       <c r="O29">
-        <v>0.3957448629795918</v>
+        <v>0.3943975449795918</v>
       </c>
       <c r="P29">
-        <v>0.9234046802857142</v>
+        <v>0.9202609382857143</v>
       </c>
       <c r="Q29">
-        <v>1.003404680285714</v>
+        <v>1.000260938285714</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.2001323897462764</v>
+        <v>0.2017650924548725</v>
       </c>
       <c r="T29">
-        <v>1.076073721858037</v>
+        <v>1.087457647702865</v>
       </c>
       <c r="U29">
         <v>0.0518</v>
@@ -3691,7 +3691,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>11.87881045706529</v>
+        <v>11.45456722645581</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3699,22 +3699,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1554236665675082</v>
+        <v>0.1549604886202348</v>
       </c>
       <c r="C30">
-        <v>7.310537449657923</v>
+        <v>7.258763707792006</v>
       </c>
       <c r="D30">
-        <v>8.749137449657923</v>
+        <v>8.784063707792006</v>
       </c>
       <c r="E30">
-        <v>-1.0224</v>
+        <v>-0.9356999999999998</v>
       </c>
       <c r="F30">
-        <v>2.4276</v>
+        <v>2.5143</v>
       </c>
       <c r="G30">
         <v>0.989</v>
@@ -3735,28 +3735,28 @@
         <v>1.440408163265306</v>
       </c>
       <c r="M30">
-        <v>0.12574968</v>
+        <v>0.13024074</v>
       </c>
       <c r="N30">
-        <v>1.314658483265306</v>
+        <v>1.310167423265306</v>
       </c>
       <c r="O30">
-        <v>0.3943975449795918</v>
+        <v>0.3930502269795918</v>
       </c>
       <c r="P30">
-        <v>0.9202609382857143</v>
+        <v>0.9171171962857142</v>
       </c>
       <c r="Q30">
-        <v>1.000260938285714</v>
+        <v>0.9971171962857143</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.2017650924548725</v>
+        <v>0.203443786789063</v>
       </c>
       <c r="T30">
-        <v>1.087457647702865</v>
+        <v>1.099162247515154</v>
       </c>
       <c r="U30">
         <v>0.0518</v>
@@ -3773,7 +3773,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>11.45456722645581</v>
+        <v>11.05958214968147</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3781,22 +3781,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1549604886202348</v>
+        <v>0.1544973106729612</v>
       </c>
       <c r="C31">
-        <v>7.258763707792006</v>
+        <v>7.207269932403942</v>
       </c>
       <c r="D31">
-        <v>8.784063707792006</v>
+        <v>8.819269932403941</v>
       </c>
       <c r="E31">
-        <v>-0.9357000000000002</v>
+        <v>-0.8490000000000002</v>
       </c>
       <c r="F31">
-        <v>2.5143</v>
+        <v>2.601</v>
       </c>
       <c r="G31">
         <v>0.989</v>
@@ -3817,28 +3817,28 @@
         <v>1.440408163265306</v>
       </c>
       <c r="M31">
-        <v>0.13024074</v>
+        <v>0.1347318</v>
       </c>
       <c r="N31">
-        <v>1.310167423265306</v>
+        <v>1.305676363265306</v>
       </c>
       <c r="O31">
-        <v>0.3930502269795918</v>
+        <v>0.3917029089795918</v>
       </c>
       <c r="P31">
-        <v>0.9171171962857142</v>
+        <v>0.9139734542857143</v>
       </c>
       <c r="Q31">
-        <v>0.9971171962857143</v>
+        <v>0.9939734542857144</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.203443786789063</v>
+        <v>0.2051704438185161</v>
       </c>
       <c r="T31">
-        <v>1.099162247515154</v>
+        <v>1.111201264464937</v>
       </c>
       <c r="U31">
         <v>0.0518</v>
@@ -3855,7 +3855,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>11.05958214968148</v>
+        <v>10.69092941135876</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3863,22 +3863,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1544973106729612</v>
+        <v>0.1540341327256877</v>
       </c>
       <c r="C32">
-        <v>7.207269932403942</v>
+        <v>7.156059503327965</v>
       </c>
       <c r="D32">
-        <v>8.819269932403941</v>
+        <v>8.854759503327964</v>
       </c>
       <c r="E32">
-        <v>-0.8490000000000002</v>
+        <v>-0.7623000000000002</v>
       </c>
       <c r="F32">
-        <v>2.601</v>
+        <v>2.6877</v>
       </c>
       <c r="G32">
         <v>0.989</v>
@@ -3899,28 +3899,28 @@
         <v>1.440408163265306</v>
       </c>
       <c r="M32">
-        <v>0.1347318</v>
+        <v>0.13922286</v>
       </c>
       <c r="N32">
-        <v>1.305676363265306</v>
+        <v>1.301185303265306</v>
       </c>
       <c r="O32">
-        <v>0.3917029089795918</v>
+        <v>0.3903555909795918</v>
       </c>
       <c r="P32">
-        <v>0.9139734542857143</v>
+        <v>0.9108297122857143</v>
       </c>
       <c r="Q32">
-        <v>0.9939734542857144</v>
+        <v>0.9908297122857144</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.2051704438185161</v>
+        <v>0.2069471488778083</v>
       </c>
       <c r="T32">
-        <v>1.111201264464937</v>
+        <v>1.123589238427756</v>
       </c>
       <c r="U32">
         <v>0.0518</v>
@@ -3937,7 +3937,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>10.69092941135876</v>
+        <v>10.34606072066977</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3945,22 +3945,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1540341327256877</v>
+        <v>0.1535709547784143</v>
       </c>
       <c r="C33">
-        <v>7.156059503327965</v>
+        <v>7.105135855021206</v>
       </c>
       <c r="D33">
-        <v>8.854759503327964</v>
+        <v>8.890535855021206</v>
       </c>
       <c r="E33">
-        <v>-0.7623000000000002</v>
+        <v>-0.6756000000000002</v>
       </c>
       <c r="F33">
-        <v>2.6877</v>
+        <v>2.7744</v>
       </c>
       <c r="G33">
         <v>0.989</v>
@@ -3981,28 +3981,28 @@
         <v>1.440408163265306</v>
       </c>
       <c r="M33">
-        <v>0.13922286</v>
+        <v>0.14371392</v>
       </c>
       <c r="N33">
-        <v>1.301185303265306</v>
+        <v>1.296694243265306</v>
       </c>
       <c r="O33">
-        <v>0.3903555909795918</v>
+        <v>0.3890082729795918</v>
       </c>
       <c r="P33">
-        <v>0.9108297122857143</v>
+        <v>0.9076859702857143</v>
       </c>
       <c r="Q33">
-        <v>0.9908297122857144</v>
+        <v>0.9876859702857144</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.2069471488778083</v>
+        <v>0.2087761099682563</v>
       </c>
       <c r="T33">
-        <v>1.123589238427756</v>
+        <v>1.136341564565953</v>
       </c>
       <c r="U33">
         <v>0.0518</v>
@@ -4019,7 +4019,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>10.34606072066977</v>
+        <v>10.02274632314884</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4027,22 +4027,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1535709547784143</v>
+        <v>0.1535004768311407</v>
       </c>
       <c r="C34">
-        <v>7.105135855021206</v>
+        <v>7.023905002974054</v>
       </c>
       <c r="D34">
-        <v>8.890535855021206</v>
+        <v>8.896005002974054</v>
       </c>
       <c r="E34">
-        <v>-0.6756000000000002</v>
+        <v>-0.5889000000000002</v>
       </c>
       <c r="F34">
-        <v>2.7744</v>
+        <v>2.8611</v>
       </c>
       <c r="G34">
         <v>0.989</v>
@@ -4063,45 +4063,45 @@
         <v>1.440408163265306</v>
       </c>
       <c r="M34">
-        <v>0.14371392</v>
+        <v>0.15306885</v>
       </c>
       <c r="N34">
-        <v>1.296694243265306</v>
+        <v>1.287339313265306</v>
       </c>
       <c r="O34">
-        <v>0.3890082729795918</v>
+        <v>0.3862017939795918</v>
       </c>
       <c r="P34">
-        <v>0.9076859702857143</v>
+        <v>0.9011375192857143</v>
       </c>
       <c r="Q34">
-        <v>0.9876859702857144</v>
+        <v>0.9811375192857144</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.2087761099682563</v>
+        <v>0.2106596669121504</v>
       </c>
       <c r="T34">
-        <v>1.136341564565953</v>
+        <v>1.149474557156037</v>
       </c>
       <c r="U34">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V34">
         <v>0.3</v>
       </c>
       <c r="W34">
-        <v>0.03625999999999999</v>
+        <v>0.03745</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y34">
-        <v>10.02274632314884</v>
+        <v>9.41019785060975</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4109,22 +4109,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1535004768311407</v>
+        <v>0.1530491988838672</v>
       </c>
       <c r="C35">
-        <v>7.023905002974054</v>
+        <v>6.972384665448518</v>
       </c>
       <c r="D35">
-        <v>8.896005002974054</v>
+        <v>8.931184665448518</v>
       </c>
       <c r="E35">
-        <v>-0.5889000000000002</v>
+        <v>-0.5022000000000002</v>
       </c>
       <c r="F35">
-        <v>2.8611</v>
+        <v>2.9478</v>
       </c>
       <c r="G35">
         <v>0.989</v>
@@ -4145,28 +4145,28 @@
         <v>1.440408163265306</v>
       </c>
       <c r="M35">
-        <v>0.15306885</v>
+        <v>0.1577073</v>
       </c>
       <c r="N35">
-        <v>1.287339313265306</v>
+        <v>1.282700863265306</v>
       </c>
       <c r="O35">
-        <v>0.3862017939795918</v>
+        <v>0.3848102589795918</v>
       </c>
       <c r="P35">
-        <v>0.9011375192857143</v>
+        <v>0.8978906042857142</v>
       </c>
       <c r="Q35">
-        <v>0.9811375192857144</v>
+        <v>0.9778906042857143</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.2106596669121504</v>
+        <v>0.2126003013391928</v>
       </c>
       <c r="T35">
-        <v>1.149474557156037</v>
+        <v>1.163005519218547</v>
       </c>
       <c r="U35">
         <v>0.0535</v>
@@ -4183,7 +4183,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>9.41019785060975</v>
+        <v>9.133427325591816</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4191,22 +4191,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1530491988838672</v>
+        <v>0.1525979209365937</v>
       </c>
       <c r="C36">
-        <v>6.972384665448518</v>
+        <v>6.921143671799933</v>
       </c>
       <c r="D36">
-        <v>8.931184665448518</v>
+        <v>8.966643671799932</v>
       </c>
       <c r="E36">
-        <v>-0.5022000000000002</v>
+        <v>-0.4154999999999998</v>
       </c>
       <c r="F36">
-        <v>2.9478</v>
+        <v>3.0345</v>
       </c>
       <c r="G36">
         <v>0.989</v>
@@ -4227,28 +4227,28 @@
         <v>1.440408163265306</v>
       </c>
       <c r="M36">
-        <v>0.1577073</v>
+        <v>0.16234575</v>
       </c>
       <c r="N36">
-        <v>1.282700863265306</v>
+        <v>1.278062413265306</v>
       </c>
       <c r="O36">
-        <v>0.3848102589795918</v>
+        <v>0.3834187239795918</v>
       </c>
       <c r="P36">
-        <v>0.8978906042857142</v>
+        <v>0.8946436892857141</v>
       </c>
       <c r="Q36">
-        <v>0.9778906042857143</v>
+        <v>0.9746436892857142</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.2126003013391928</v>
+        <v>0.2146006475947596</v>
       </c>
       <c r="T36">
-        <v>1.163005519218547</v>
+        <v>1.176952818575288</v>
       </c>
       <c r="U36">
         <v>0.0535</v>
@@ -4265,7 +4265,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>9.133427325591816</v>
+        <v>8.872472259146335</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4273,22 +4273,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1525979209365937</v>
+        <v>0.1521466429893202</v>
       </c>
       <c r="C37">
-        <v>6.921143671799933</v>
+        <v>6.870185362483044</v>
       </c>
       <c r="D37">
-        <v>8.966643671799932</v>
+        <v>9.002385362483043</v>
       </c>
       <c r="E37">
-        <v>-0.4154999999999998</v>
+        <v>-0.3287999999999998</v>
       </c>
       <c r="F37">
-        <v>3.0345</v>
+        <v>3.1212</v>
       </c>
       <c r="G37">
         <v>0.989</v>
@@ -4309,28 +4309,28 @@
         <v>1.440408163265306</v>
       </c>
       <c r="M37">
-        <v>0.16234575</v>
+        <v>0.1669842</v>
       </c>
       <c r="N37">
-        <v>1.278062413265306</v>
+        <v>1.273423963265306</v>
       </c>
       <c r="O37">
-        <v>0.3834187239795918</v>
+        <v>0.3820271889795918</v>
       </c>
       <c r="P37">
-        <v>0.8946436892857141</v>
+        <v>0.8913967742857142</v>
       </c>
       <c r="Q37">
-        <v>0.9746436892857142</v>
+        <v>0.9713967742857142</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.2146006475947596</v>
+        <v>0.2166635046708129</v>
       </c>
       <c r="T37">
-        <v>1.176952818575288</v>
+        <v>1.191335971036927</v>
       </c>
       <c r="U37">
         <v>0.0535</v>
@@ -4347,7 +4347,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>8.872472259146335</v>
+        <v>8.626014696392268</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4355,22 +4355,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1521466429893203</v>
+        <v>0.1516953650420468</v>
       </c>
       <c r="C38">
-        <v>6.870185362483042</v>
+        <v>6.819513131426911</v>
       </c>
       <c r="D38">
-        <v>9.002385362483041</v>
+        <v>9.03841313142691</v>
       </c>
       <c r="E38">
-        <v>-0.3288000000000002</v>
+        <v>-0.2421000000000002</v>
       </c>
       <c r="F38">
-        <v>3.1212</v>
+        <v>3.2079</v>
       </c>
       <c r="G38">
         <v>0.989</v>
@@ -4391,28 +4391,28 @@
         <v>1.440408163265306</v>
       </c>
       <c r="M38">
-        <v>0.1669842</v>
+        <v>0.17162265</v>
       </c>
       <c r="N38">
-        <v>1.273423963265306</v>
+        <v>1.268785513265306</v>
       </c>
       <c r="O38">
-        <v>0.3820271889795918</v>
+        <v>0.3806356539795918</v>
       </c>
       <c r="P38">
-        <v>0.8913967742857143</v>
+        <v>0.8881498592857142</v>
       </c>
       <c r="Q38">
-        <v>0.9713967742857144</v>
+        <v>0.9681498592857143</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.2166635046708129</v>
+        <v>0.2187918492730901</v>
       </c>
       <c r="T38">
-        <v>1.191335971036927</v>
+        <v>1.206175731513222</v>
       </c>
       <c r="U38">
         <v>0.0535</v>
@@ -4429,7 +4429,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>8.626014696392271</v>
+        <v>8.392879164057344</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4437,22 +4437,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1516953650420468</v>
+        <v>0.1512440870947732</v>
       </c>
       <c r="C39">
-        <v>6.819513131426911</v>
+        <v>6.769130427109267</v>
       </c>
       <c r="D39">
-        <v>9.03841313142691</v>
+        <v>9.074730427109266</v>
       </c>
       <c r="E39">
-        <v>-0.2421000000000002</v>
+        <v>-0.1554000000000002</v>
       </c>
       <c r="F39">
-        <v>3.2079</v>
+        <v>3.2946</v>
       </c>
       <c r="G39">
         <v>0.989</v>
@@ -4473,28 +4473,28 @@
         <v>1.440408163265306</v>
       </c>
       <c r="M39">
-        <v>0.17162265</v>
+        <v>0.1762611</v>
       </c>
       <c r="N39">
-        <v>1.268785513265306</v>
+        <v>1.264147063265306</v>
       </c>
       <c r="O39">
-        <v>0.3806356539795918</v>
+        <v>0.3792441189795918</v>
       </c>
       <c r="P39">
-        <v>0.8881498592857142</v>
+        <v>0.8849029442857141</v>
       </c>
       <c r="Q39">
-        <v>0.9681498592857143</v>
+        <v>0.9649029442857142</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.2187918492730901</v>
+        <v>0.2209888501528601</v>
       </c>
       <c r="T39">
-        <v>1.206175731513222</v>
+        <v>1.221494193940365</v>
       </c>
       <c r="U39">
         <v>0.0535</v>
@@ -4511,7 +4511,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>8.392879164057344</v>
+        <v>8.172013922897939</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4519,22 +4519,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1512440870947732</v>
+        <v>0.1507928091474998</v>
       </c>
       <c r="C40">
-        <v>6.769130427109267</v>
+        <v>6.719040753656818</v>
       </c>
       <c r="D40">
-        <v>9.074730427109266</v>
+        <v>9.111340753656817</v>
       </c>
       <c r="E40">
-        <v>-0.1554000000000002</v>
+        <v>-0.06870000000000021</v>
       </c>
       <c r="F40">
-        <v>3.2946</v>
+        <v>3.3813</v>
       </c>
       <c r="G40">
         <v>0.989</v>
@@ -4555,28 +4555,28 @@
         <v>1.440408163265306</v>
       </c>
       <c r="M40">
-        <v>0.1762611</v>
+        <v>0.18089955</v>
       </c>
       <c r="N40">
-        <v>1.264147063265306</v>
+        <v>1.259508613265306</v>
       </c>
       <c r="O40">
-        <v>0.3792441189795918</v>
+        <v>0.3778525839795918</v>
       </c>
       <c r="P40">
-        <v>0.8849029442857141</v>
+        <v>0.8816560292857143</v>
       </c>
       <c r="Q40">
-        <v>0.9649029442857142</v>
+        <v>0.9616560292857144</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.2209888501528601</v>
+        <v>0.2232578838483603</v>
       </c>
       <c r="T40">
-        <v>1.221494193940365</v>
+        <v>1.23731490103725</v>
       </c>
       <c r="U40">
         <v>0.0535</v>
@@ -4593,7 +4593,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>8.172013922897939</v>
+        <v>7.962475104362096</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4601,22 +4601,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1507928091474998</v>
+        <v>0.1503415312002263</v>
       </c>
       <c r="C41">
-        <v>6.719040753656818</v>
+        <v>6.669247671972352</v>
       </c>
       <c r="D41">
-        <v>9.111340753656817</v>
+        <v>9.148247671972351</v>
       </c>
       <c r="E41">
-        <v>-0.06870000000000021</v>
+        <v>0.01799999999999979</v>
       </c>
       <c r="F41">
-        <v>3.3813</v>
+        <v>3.468</v>
       </c>
       <c r="G41">
         <v>0.989</v>
@@ -4637,28 +4637,28 @@
         <v>1.440408163265306</v>
       </c>
       <c r="M41">
-        <v>0.18089955</v>
+        <v>0.185538</v>
       </c>
       <c r="N41">
-        <v>1.259508613265306</v>
+        <v>1.254870163265306</v>
       </c>
       <c r="O41">
-        <v>0.3778525839795918</v>
+        <v>0.3764610489795918</v>
       </c>
       <c r="P41">
-        <v>0.8816560292857143</v>
+        <v>0.8784091142857142</v>
       </c>
       <c r="Q41">
-        <v>0.9616560292857144</v>
+        <v>0.9584091142857143</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.2232578838483603</v>
+        <v>0.2256025520003771</v>
       </c>
       <c r="T41">
-        <v>1.23731490103725</v>
+        <v>1.253662965037365</v>
       </c>
       <c r="U41">
         <v>0.0535</v>
@@ -4675,7 +4675,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>7.962475104362096</v>
+        <v>7.763413226753043</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4683,22 +4683,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1503415312002263</v>
+        <v>0.1501198532529527</v>
       </c>
       <c r="C42">
-        <v>6.669247671972352</v>
+        <v>6.6007869144655</v>
       </c>
       <c r="D42">
-        <v>9.148247671972351</v>
+        <v>9.1664869144655</v>
       </c>
       <c r="E42">
-        <v>0.01799999999999979</v>
+        <v>0.1047000000000002</v>
       </c>
       <c r="F42">
-        <v>3.468</v>
+        <v>3.5547</v>
       </c>
       <c r="G42">
         <v>0.989</v>
@@ -4719,45 +4719,45 @@
         <v>1.440408163265306</v>
       </c>
       <c r="M42">
-        <v>0.185538</v>
+        <v>0.19302021</v>
       </c>
       <c r="N42">
-        <v>1.254870163265306</v>
+        <v>1.247387953265306</v>
       </c>
       <c r="O42">
-        <v>0.3764610489795918</v>
+        <v>0.3742163859795918</v>
       </c>
       <c r="P42">
-        <v>0.8784091142857142</v>
+        <v>0.8731715672857143</v>
       </c>
       <c r="Q42">
-        <v>0.9584091142857143</v>
+        <v>0.9531715672857144</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.2256025520003771</v>
+        <v>0.2280267004287335</v>
       </c>
       <c r="T42">
-        <v>1.253662965037365</v>
+        <v>1.2705652006985</v>
       </c>
       <c r="U42">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V42">
         <v>0.3</v>
       </c>
       <c r="W42">
-        <v>0.03745</v>
+        <v>0.03801</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y42">
-        <v>7.763413226753043</v>
+        <v>7.462473298859772</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4765,22 +4765,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1501198532529527</v>
+        <v>0.1496741753056792</v>
       </c>
       <c r="C43">
-        <v>6.6007869144655</v>
+        <v>6.550977433909777</v>
       </c>
       <c r="D43">
-        <v>9.1664869144655</v>
+        <v>9.203377433909777</v>
       </c>
       <c r="E43">
-        <v>0.1047000000000002</v>
+        <v>0.1914000000000002</v>
       </c>
       <c r="F43">
-        <v>3.5547</v>
+        <v>3.6414</v>
       </c>
       <c r="G43">
         <v>0.989</v>
@@ -4801,28 +4801,28 @@
         <v>1.440408163265306</v>
       </c>
       <c r="M43">
-        <v>0.19302021</v>
+        <v>0.19772802</v>
       </c>
       <c r="N43">
-        <v>1.247387953265306</v>
+        <v>1.242680143265306</v>
       </c>
       <c r="O43">
-        <v>0.3742163859795918</v>
+        <v>0.3728040429795918</v>
       </c>
       <c r="P43">
-        <v>0.8731715672857143</v>
+        <v>0.8698761002857143</v>
       </c>
       <c r="Q43">
-        <v>0.9531715672857144</v>
+        <v>0.9498761002857143</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.2280267004287335</v>
+        <v>0.2305344401822056</v>
       </c>
       <c r="T43">
-        <v>1.2705652006985</v>
+        <v>1.288050272072088</v>
       </c>
       <c r="U43">
         <v>0.0543</v>
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>7.462473298859772</v>
+        <v>7.284795363172634</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4847,22 +4847,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1496741753056793</v>
+        <v>0.1492284973584058</v>
       </c>
       <c r="C44">
-        <v>6.550977433909773</v>
+        <v>6.501466084917809</v>
       </c>
       <c r="D44">
-        <v>9.203377433909772</v>
+        <v>9.240566084917807</v>
       </c>
       <c r="E44">
-        <v>0.1913999999999998</v>
+        <v>0.2780999999999998</v>
       </c>
       <c r="F44">
-        <v>3.6414</v>
+        <v>3.7281</v>
       </c>
       <c r="G44">
         <v>0.989</v>
@@ -4883,28 +4883,28 @@
         <v>1.440408163265306</v>
       </c>
       <c r="M44">
-        <v>0.19772802</v>
+        <v>0.20243583</v>
       </c>
       <c r="N44">
-        <v>1.242680143265306</v>
+        <v>1.237972333265306</v>
       </c>
       <c r="O44">
-        <v>0.3728040429795918</v>
+        <v>0.3713916999795918</v>
       </c>
       <c r="P44">
-        <v>0.8698761002857143</v>
+        <v>0.8665806332857142</v>
       </c>
       <c r="Q44">
-        <v>0.9498761002857143</v>
+        <v>0.9465806332857143</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.2305344401822056</v>
+        <v>0.2331301708042206</v>
       </c>
       <c r="T44">
-        <v>1.288050272072088</v>
+        <v>1.306148854721943</v>
       </c>
       <c r="U44">
         <v>0.0543</v>
@@ -4921,7 +4921,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>7.284795363172635</v>
+        <v>7.115381517517458</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4929,22 +4929,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1492284973584058</v>
+        <v>0.1487828194111322</v>
       </c>
       <c r="C45">
-        <v>6.501466084917809</v>
+        <v>6.452256496187729</v>
       </c>
       <c r="D45">
-        <v>9.240566084917807</v>
+        <v>9.278056496187729</v>
       </c>
       <c r="E45">
-        <v>0.2780999999999998</v>
+        <v>0.3647999999999998</v>
       </c>
       <c r="F45">
-        <v>3.7281</v>
+        <v>3.8148</v>
       </c>
       <c r="G45">
         <v>0.989</v>
@@ -4965,28 +4965,28 @@
         <v>1.440408163265306</v>
       </c>
       <c r="M45">
-        <v>0.20243583</v>
+        <v>0.20714364</v>
       </c>
       <c r="N45">
-        <v>1.237972333265306</v>
+        <v>1.233264523265306</v>
       </c>
       <c r="O45">
-        <v>0.3713916999795918</v>
+        <v>0.3699793569795918</v>
       </c>
       <c r="P45">
-        <v>0.8665806332857142</v>
+        <v>0.8632851662857143</v>
       </c>
       <c r="Q45">
-        <v>0.9465806332857143</v>
+        <v>0.9432851662857143</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.2331301708042206</v>
+        <v>0.2358186060913076</v>
       </c>
       <c r="T45">
-        <v>1.306148854721943</v>
+        <v>1.324893815323578</v>
       </c>
       <c r="U45">
         <v>0.0543</v>
@@ -5003,7 +5003,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>7.115381517517458</v>
+        <v>6.953668301210243</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5011,22 +5011,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1487828194111322</v>
+        <v>0.1483371414638588</v>
       </c>
       <c r="C46">
-        <v>6.452256496187729</v>
+        <v>6.403352355546314</v>
       </c>
       <c r="D46">
-        <v>9.278056496187729</v>
+        <v>9.315852355546314</v>
       </c>
       <c r="E46">
-        <v>0.3647999999999998</v>
+        <v>0.4514999999999998</v>
       </c>
       <c r="F46">
-        <v>3.8148</v>
+        <v>3.9015</v>
       </c>
       <c r="G46">
         <v>0.989</v>
@@ -5047,28 +5047,28 @@
         <v>1.440408163265306</v>
       </c>
       <c r="M46">
-        <v>0.20714364</v>
+        <v>0.21185145</v>
       </c>
       <c r="N46">
-        <v>1.233264523265306</v>
+        <v>1.228556713265306</v>
       </c>
       <c r="O46">
-        <v>0.3699793569795918</v>
+        <v>0.3685670139795919</v>
       </c>
       <c r="P46">
-        <v>0.8632851662857143</v>
+        <v>0.8599896992857143</v>
       </c>
       <c r="Q46">
-        <v>0.9432851662857143</v>
+        <v>0.9399896992857144</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.2358186060913076</v>
+        <v>0.2386048026615614</v>
       </c>
       <c r="T46">
-        <v>1.324893815323578</v>
+        <v>1.344320410856182</v>
       </c>
       <c r="U46">
         <v>0.0543</v>
@@ -5085,7 +5085,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>6.953668301210243</v>
+        <v>6.799142338961127</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5093,22 +5093,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1483371414638588</v>
+        <v>0.1478914635165852</v>
       </c>
       <c r="C47">
-        <v>6.403352355546314</v>
+        <v>6.354757411158297</v>
       </c>
       <c r="D47">
-        <v>9.315852355546314</v>
+        <v>9.353957411158296</v>
       </c>
       <c r="E47">
-        <v>0.4514999999999998</v>
+        <v>0.5381999999999998</v>
       </c>
       <c r="F47">
-        <v>3.9015</v>
+        <v>3.9882</v>
       </c>
       <c r="G47">
         <v>0.989</v>
@@ -5129,28 +5129,28 @@
         <v>1.440408163265306</v>
       </c>
       <c r="M47">
-        <v>0.21185145</v>
+        <v>0.21655926</v>
       </c>
       <c r="N47">
-        <v>1.228556713265306</v>
+        <v>1.223848903265306</v>
       </c>
       <c r="O47">
-        <v>0.3685670139795919</v>
+        <v>0.3671546709795918</v>
       </c>
       <c r="P47">
-        <v>0.8599896992857143</v>
+        <v>0.8566942322857143</v>
       </c>
       <c r="Q47">
-        <v>0.9399896992857144</v>
+        <v>0.9366942322857144</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.2386048026615614</v>
+        <v>0.2414941916973801</v>
       </c>
       <c r="T47">
-        <v>1.344320410856182</v>
+        <v>1.36446650992703</v>
       </c>
       <c r="U47">
         <v>0.0543</v>
@@ -5167,7 +5167,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>6.799142338961127</v>
+        <v>6.651334896809797</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5175,22 +5175,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1478914635165852</v>
+        <v>0.1474457855693118</v>
       </c>
       <c r="C48">
-        <v>6.354757411158297</v>
+        <v>6.306475472765428</v>
       </c>
       <c r="D48">
-        <v>9.353957411158296</v>
+        <v>9.392375472765428</v>
       </c>
       <c r="E48">
-        <v>0.5381999999999998</v>
+        <v>0.6249000000000002</v>
       </c>
       <c r="F48">
-        <v>3.9882</v>
+        <v>4.0749</v>
       </c>
       <c r="G48">
         <v>0.989</v>
@@ -5211,28 +5211,28 @@
         <v>1.440408163265306</v>
       </c>
       <c r="M48">
-        <v>0.21655926</v>
+        <v>0.22126707</v>
       </c>
       <c r="N48">
-        <v>1.223848903265306</v>
+        <v>1.219141093265306</v>
       </c>
       <c r="O48">
-        <v>0.3671546709795918</v>
+        <v>0.3657423279795918</v>
       </c>
       <c r="P48">
-        <v>0.8566942322857143</v>
+        <v>0.8533987652857142</v>
       </c>
       <c r="Q48">
-        <v>0.9366942322857144</v>
+        <v>0.9333987652857143</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.2414941916973801</v>
+        <v>0.2444926142817203</v>
       </c>
       <c r="T48">
-        <v>1.36446650992703</v>
+        <v>1.385372839151496</v>
       </c>
       <c r="U48">
         <v>0.0543</v>
@@ -5249,7 +5249,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>6.651334896809797</v>
+        <v>6.509817133047886</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5257,22 +5257,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1474457855693118</v>
+        <v>0.1470001076220383</v>
       </c>
       <c r="C49">
-        <v>6.306475472765428</v>
+        <v>6.258510412956243</v>
       </c>
       <c r="D49">
-        <v>9.392375472765428</v>
+        <v>9.431110412956242</v>
       </c>
       <c r="E49">
-        <v>0.6249000000000002</v>
+        <v>0.7115999999999998</v>
       </c>
       <c r="F49">
-        <v>4.0749</v>
+        <v>4.1616</v>
       </c>
       <c r="G49">
         <v>0.989</v>
@@ -5293,28 +5293,28 @@
         <v>1.440408163265306</v>
       </c>
       <c r="M49">
-        <v>0.22126707</v>
+        <v>0.22597488</v>
       </c>
       <c r="N49">
-        <v>1.219141093265306</v>
+        <v>1.214433283265306</v>
       </c>
       <c r="O49">
-        <v>0.3657423279795918</v>
+        <v>0.3643299849795918</v>
       </c>
       <c r="P49">
-        <v>0.8533987652857142</v>
+        <v>0.8501032982857142</v>
       </c>
       <c r="Q49">
-        <v>0.9333987652857143</v>
+        <v>0.9301032982857143</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.2444926142817203</v>
+        <v>0.2476063608116121</v>
       </c>
       <c r="T49">
-        <v>1.385372839151496</v>
+        <v>1.407083257961517</v>
       </c>
       <c r="U49">
         <v>0.0543</v>
@@ -5331,7 +5331,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>6.509817133047886</v>
+        <v>6.374195942776056</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5339,22 +5339,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1470001076220383</v>
+        <v>0.1465544296747648</v>
       </c>
       <c r="C50">
-        <v>6.258510412956243</v>
+        <v>6.210866168467329</v>
       </c>
       <c r="D50">
-        <v>9.431110412956242</v>
+        <v>9.470166168467328</v>
       </c>
       <c r="E50">
-        <v>0.7115999999999998</v>
+        <v>0.7982999999999993</v>
       </c>
       <c r="F50">
-        <v>4.1616</v>
+        <v>4.2483</v>
       </c>
       <c r="G50">
         <v>0.989</v>
@@ -5375,28 +5375,28 @@
         <v>1.440408163265306</v>
       </c>
       <c r="M50">
-        <v>0.22597488</v>
+        <v>0.23068269</v>
       </c>
       <c r="N50">
-        <v>1.214433283265306</v>
+        <v>1.209725473265306</v>
       </c>
       <c r="O50">
-        <v>0.3643299849795918</v>
+        <v>0.3629176419795919</v>
       </c>
       <c r="P50">
-        <v>0.8501032982857142</v>
+        <v>0.8468078312857144</v>
       </c>
       <c r="Q50">
-        <v>0.9301032982857143</v>
+        <v>0.9268078312857144</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.2476063608116121</v>
+        <v>0.2508422150485584</v>
       </c>
       <c r="T50">
-        <v>1.407083257961517</v>
+        <v>1.429645065744481</v>
       </c>
       <c r="U50">
         <v>0.0543</v>
@@ -5413,7 +5413,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>6.374195942776056</v>
+        <v>6.244110311290831</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5421,22 +5421,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1465544296747648</v>
+        <v>0.1461087517274913</v>
       </c>
       <c r="C51">
-        <v>6.210866168467329</v>
+        <v>6.163546741517105</v>
       </c>
       <c r="D51">
-        <v>9.470166168467328</v>
+        <v>9.509546741517104</v>
       </c>
       <c r="E51">
-        <v>0.7982999999999993</v>
+        <v>0.8849999999999998</v>
       </c>
       <c r="F51">
-        <v>4.2483</v>
+        <v>4.335</v>
       </c>
       <c r="G51">
         <v>0.989</v>
@@ -5457,28 +5457,28 @@
         <v>1.440408163265306</v>
       </c>
       <c r="M51">
-        <v>0.23068269</v>
+        <v>0.2353905</v>
       </c>
       <c r="N51">
-        <v>1.209725473265306</v>
+        <v>1.205017663265306</v>
       </c>
       <c r="O51">
-        <v>0.3629176419795919</v>
+        <v>0.3615052989795918</v>
       </c>
       <c r="P51">
-        <v>0.8468078312857144</v>
+        <v>0.8435123642857143</v>
       </c>
       <c r="Q51">
-        <v>0.9268078312857144</v>
+        <v>0.9235123642857144</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.2508422150485584</v>
+        <v>0.2542075034549826</v>
       </c>
       <c r="T51">
-        <v>1.429645065744481</v>
+        <v>1.453109345838763</v>
       </c>
       <c r="U51">
         <v>0.0543</v>
@@ -5495,7 +5495,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>6.244110311290831</v>
+        <v>6.119228105065013</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5503,22 +5503,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1461087517274913</v>
+        <v>0.1460200737802178</v>
       </c>
       <c r="C52">
-        <v>6.163546741517105</v>
+        <v>6.084721517763966</v>
       </c>
       <c r="D52">
-        <v>9.509546741517104</v>
+        <v>9.517421517763966</v>
       </c>
       <c r="E52">
-        <v>0.8849999999999998</v>
+        <v>0.9717000000000002</v>
       </c>
       <c r="F52">
-        <v>4.335</v>
+        <v>4.4217</v>
       </c>
       <c r="G52">
         <v>0.989</v>
@@ -5539,45 +5539,45 @@
         <v>1.440408163265306</v>
       </c>
       <c r="M52">
-        <v>0.2353905</v>
+        <v>0.24452001</v>
       </c>
       <c r="N52">
-        <v>1.205017663265306</v>
+        <v>1.195888153265306</v>
       </c>
       <c r="O52">
-        <v>0.3615052989795918</v>
+        <v>0.3587664459795918</v>
       </c>
       <c r="P52">
-        <v>0.8435123642857143</v>
+        <v>0.8371217072857142</v>
       </c>
       <c r="Q52">
-        <v>0.9235123642857144</v>
+        <v>0.9171217072857143</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.2542075034549826</v>
+        <v>0.257710150571873</v>
       </c>
       <c r="T52">
-        <v>1.453109345838763</v>
+        <v>1.47753135165118</v>
       </c>
       <c r="U52">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V52">
         <v>0.3</v>
       </c>
       <c r="W52">
-        <v>0.03801</v>
+        <v>0.03871</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y52">
-        <v>6.119228105065013</v>
+        <v>5.890757829043545</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5585,22 +5585,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1460200737802178</v>
+        <v>0.1455813958329443</v>
       </c>
       <c r="C53">
-        <v>6.084721517763966</v>
+        <v>6.037169610090478</v>
       </c>
       <c r="D53">
-        <v>9.517421517763966</v>
+        <v>9.556569610090477</v>
       </c>
       <c r="E53">
-        <v>0.9717000000000002</v>
+        <v>1.0584</v>
       </c>
       <c r="F53">
-        <v>4.4217</v>
+        <v>4.5084</v>
       </c>
       <c r="G53">
         <v>0.989</v>
@@ -5621,28 +5621,28 @@
         <v>1.440408163265306</v>
       </c>
       <c r="M53">
-        <v>0.24452001</v>
+        <v>0.24931452</v>
       </c>
       <c r="N53">
-        <v>1.195888153265306</v>
+        <v>1.191093643265306</v>
       </c>
       <c r="O53">
-        <v>0.3587664459795918</v>
+        <v>0.3573280929795918</v>
       </c>
       <c r="P53">
-        <v>0.8371217072857142</v>
+        <v>0.8337655502857142</v>
       </c>
       <c r="Q53">
-        <v>0.9171217072857143</v>
+        <v>0.9137655502857143</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.257710150571873</v>
+        <v>0.2613587413186339</v>
       </c>
       <c r="T53">
-        <v>1.47753135165118</v>
+        <v>1.502970941039113</v>
       </c>
       <c r="U53">
         <v>0.0553</v>
@@ -5659,7 +5659,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>5.890757829043545</v>
+        <v>5.777474024638862</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5667,22 +5667,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1455813958329443</v>
+        <v>0.1451427178856708</v>
       </c>
       <c r="C54">
-        <v>6.037169610090478</v>
+        <v>5.989941088979924</v>
       </c>
       <c r="D54">
-        <v>9.556569610090477</v>
+        <v>9.596041088979923</v>
       </c>
       <c r="E54">
-        <v>1.0584</v>
+        <v>1.1451</v>
       </c>
       <c r="F54">
-        <v>4.5084</v>
+        <v>4.5951</v>
       </c>
       <c r="G54">
         <v>0.989</v>
@@ -5703,28 +5703,28 @@
         <v>1.440408163265306</v>
       </c>
       <c r="M54">
-        <v>0.24931452</v>
+        <v>0.25410903</v>
       </c>
       <c r="N54">
-        <v>1.191093643265306</v>
+        <v>1.186299133265306</v>
       </c>
       <c r="O54">
-        <v>0.3573280929795918</v>
+        <v>0.3558897399795918</v>
       </c>
       <c r="P54">
-        <v>0.8337655502857142</v>
+        <v>0.8304093932857143</v>
       </c>
       <c r="Q54">
-        <v>0.9137655502857143</v>
+        <v>0.9104093932857144</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.2613587413186339</v>
+        <v>0.265162591246108</v>
       </c>
       <c r="T54">
-        <v>1.502970941039113</v>
+        <v>1.529493066145682</v>
       </c>
       <c r="U54">
         <v>0.0553</v>
@@ -5741,7 +5741,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>5.777474024638862</v>
+        <v>5.668465080777751</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5749,22 +5749,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1451427178856708</v>
+        <v>0.1447040399383973</v>
       </c>
       <c r="C55">
-        <v>5.989941088979924</v>
+        <v>5.943039978099727</v>
       </c>
       <c r="D55">
-        <v>9.596041088979923</v>
+        <v>9.635839978099726</v>
       </c>
       <c r="E55">
-        <v>1.1451</v>
+        <v>1.2318</v>
       </c>
       <c r="F55">
-        <v>4.5951</v>
+        <v>4.6818</v>
       </c>
       <c r="G55">
         <v>0.989</v>
@@ -5785,28 +5785,28 @@
         <v>1.440408163265306</v>
       </c>
       <c r="M55">
-        <v>0.25410903</v>
+        <v>0.25890354</v>
       </c>
       <c r="N55">
-        <v>1.186299133265306</v>
+        <v>1.181504623265306</v>
       </c>
       <c r="O55">
-        <v>0.3558897399795918</v>
+        <v>0.3544513869795918</v>
       </c>
       <c r="P55">
-        <v>0.8304093932857143</v>
+        <v>0.8270532362857144</v>
       </c>
       <c r="Q55">
-        <v>0.9104093932857144</v>
+        <v>0.9070532362857144</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.265162591246108</v>
+        <v>0.2691318259530375</v>
       </c>
       <c r="T55">
-        <v>1.529493066145682</v>
+        <v>1.55716832712645</v>
       </c>
       <c r="U55">
         <v>0.0553</v>
@@ -5823,7 +5823,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>5.668465080777751</v>
+        <v>5.563493505207793</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5831,22 +5831,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1447040399383973</v>
+        <v>0.1442653619911238</v>
       </c>
       <c r="C56">
-        <v>5.943039978099727</v>
+        <v>5.896470368146782</v>
       </c>
       <c r="D56">
-        <v>9.635839978099726</v>
+        <v>9.675970368146782</v>
       </c>
       <c r="E56">
-        <v>1.2318</v>
+        <v>1.3185</v>
       </c>
       <c r="F56">
-        <v>4.6818</v>
+        <v>4.7685</v>
       </c>
       <c r="G56">
         <v>0.989</v>
@@ -5867,28 +5867,28 @@
         <v>1.440408163265306</v>
       </c>
       <c r="M56">
-        <v>0.25890354</v>
+        <v>0.26369805</v>
       </c>
       <c r="N56">
-        <v>1.181504623265306</v>
+        <v>1.176710113265306</v>
       </c>
       <c r="O56">
-        <v>0.3544513869795918</v>
+        <v>0.3530130339795918</v>
       </c>
       <c r="P56">
-        <v>0.8270532362857144</v>
+        <v>0.8236970792857141</v>
       </c>
       <c r="Q56">
-        <v>0.9070532362857144</v>
+        <v>0.9036970792857142</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.2691318259530375</v>
+        <v>0.2732774710913862</v>
       </c>
       <c r="T56">
-        <v>1.55716832712645</v>
+        <v>1.586073599706363</v>
       </c>
       <c r="U56">
         <v>0.0553</v>
@@ -5905,7 +5905,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>5.563493505207793</v>
+        <v>5.462339077840378</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5913,22 +5913,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1442653619911238</v>
+        <v>0.1438266840438503</v>
       </c>
       <c r="C57">
-        <v>5.896470368146782</v>
+        <v>5.850236418249108</v>
       </c>
       <c r="D57">
-        <v>9.675970368146782</v>
+        <v>9.716436418249108</v>
       </c>
       <c r="E57">
-        <v>1.3185</v>
+        <v>1.405200000000001</v>
       </c>
       <c r="F57">
-        <v>4.7685</v>
+        <v>4.855200000000001</v>
       </c>
       <c r="G57">
         <v>0.989</v>
@@ -5949,28 +5949,28 @@
         <v>1.440408163265306</v>
       </c>
       <c r="M57">
-        <v>0.26369805</v>
+        <v>0.26849256</v>
       </c>
       <c r="N57">
-        <v>1.176710113265306</v>
+        <v>1.171915603265306</v>
       </c>
       <c r="O57">
-        <v>0.3530130339795918</v>
+        <v>0.3515746809795918</v>
       </c>
       <c r="P57">
-        <v>0.8236970792857141</v>
+        <v>0.8203409222857142</v>
       </c>
       <c r="Q57">
-        <v>0.9036970792857142</v>
+        <v>0.9003409222857143</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.2732774710913862</v>
+        <v>0.2776115546451143</v>
       </c>
       <c r="T57">
-        <v>1.586073599706363</v>
+        <v>1.616292748312635</v>
       </c>
       <c r="U57">
         <v>0.0553</v>
@@ -5987,7 +5987,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>5.462339077840378</v>
+        <v>5.364797308593228</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -5995,22 +5995,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1438266840438503</v>
+        <v>0.1433880060965768</v>
       </c>
       <c r="C58">
-        <v>5.850236418249108</v>
+        <v>5.804342357402767</v>
       </c>
       <c r="D58">
-        <v>9.716436418249108</v>
+        <v>9.757242357402767</v>
       </c>
       <c r="E58">
-        <v>1.405200000000001</v>
+        <v>1.4919</v>
       </c>
       <c r="F58">
-        <v>4.855200000000001</v>
+        <v>4.9419</v>
       </c>
       <c r="G58">
         <v>0.989</v>
@@ -6031,28 +6031,28 @@
         <v>1.440408163265306</v>
       </c>
       <c r="M58">
-        <v>0.26849256</v>
+        <v>0.27328707</v>
       </c>
       <c r="N58">
-        <v>1.171915603265306</v>
+        <v>1.167121093265306</v>
       </c>
       <c r="O58">
-        <v>0.3515746809795918</v>
+        <v>0.3501363279795918</v>
       </c>
       <c r="P58">
-        <v>0.8203409222857142</v>
+        <v>0.8169847652857143</v>
       </c>
       <c r="Q58">
-        <v>0.9003409222857143</v>
+        <v>0.8969847652857144</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.2776115546451143</v>
+        <v>0.2821472234804111</v>
       </c>
       <c r="T58">
-        <v>1.616292748312635</v>
+        <v>1.647917438714548</v>
       </c>
       <c r="U58">
         <v>0.0553</v>
@@ -6069,7 +6069,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>5.364797308593228</v>
+        <v>5.270678057565277</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6077,22 +6077,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1433880060965768</v>
+        <v>0.1429493281493033</v>
       </c>
       <c r="C59">
-        <v>5.804342357402767</v>
+        <v>5.758792485945181</v>
       </c>
       <c r="D59">
-        <v>9.757242357402767</v>
+        <v>9.798392485945181</v>
       </c>
       <c r="E59">
-        <v>1.4919</v>
+        <v>1.578600000000001</v>
       </c>
       <c r="F59">
-        <v>4.9419</v>
+        <v>5.028600000000001</v>
       </c>
       <c r="G59">
         <v>0.989</v>
@@ -6113,28 +6113,28 @@
         <v>1.440408163265306</v>
       </c>
       <c r="M59">
-        <v>0.27328707</v>
+        <v>0.2780815800000001</v>
       </c>
       <c r="N59">
-        <v>1.167121093265306</v>
+        <v>1.162326583265306</v>
       </c>
       <c r="O59">
-        <v>0.3501363279795918</v>
+        <v>0.3486979749795918</v>
       </c>
       <c r="P59">
-        <v>0.8169847652857143</v>
+        <v>0.8136286082857143</v>
       </c>
       <c r="Q59">
-        <v>0.8969847652857144</v>
+        <v>0.8936286082857143</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.2821472234804111</v>
+        <v>0.2868988765459602</v>
       </c>
       <c r="T59">
-        <v>1.647917438714548</v>
+        <v>1.681048066754648</v>
       </c>
       <c r="U59">
         <v>0.0553</v>
@@ -6151,7 +6151,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>5.270678057565277</v>
+        <v>5.179804297952082</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6159,22 +6159,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1429493281493033</v>
+        <v>0.1425106502020298</v>
       </c>
       <c r="C60">
-        <v>5.758792485945178</v>
+        <v>5.713591177065874</v>
       </c>
       <c r="D60">
-        <v>9.798392485945177</v>
+        <v>9.839891177065873</v>
       </c>
       <c r="E60">
-        <v>1.5786</v>
+        <v>1.665299999999999</v>
       </c>
       <c r="F60">
-        <v>5.0286</v>
+        <v>5.1153</v>
       </c>
       <c r="G60">
         <v>0.989</v>
@@ -6195,28 +6195,28 @@
         <v>1.440408163265306</v>
       </c>
       <c r="M60">
-        <v>0.27808158</v>
+        <v>0.28287609</v>
       </c>
       <c r="N60">
-        <v>1.162326583265306</v>
+        <v>1.157532073265306</v>
       </c>
       <c r="O60">
-        <v>0.3486979749795918</v>
+        <v>0.3472596219795918</v>
       </c>
       <c r="P60">
-        <v>0.8136286082857143</v>
+        <v>0.8102724512857142</v>
       </c>
       <c r="Q60">
-        <v>0.8936286082857143</v>
+        <v>0.8902724512857143</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.2868988765459601</v>
+        <v>0.2918823175659263</v>
       </c>
       <c r="T60">
-        <v>1.681048066754647</v>
+        <v>1.715794822991825</v>
       </c>
       <c r="U60">
         <v>0.0553</v>
@@ -6233,7 +6233,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>5.179804297952083</v>
+        <v>5.092011004766455</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6241,22 +6241,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1425106502020298</v>
+        <v>0.1420719722547563</v>
       </c>
       <c r="C61">
-        <v>5.713591177065874</v>
+        <v>5.668742878355774</v>
       </c>
       <c r="D61">
-        <v>9.839891177065873</v>
+        <v>9.881742878355773</v>
       </c>
       <c r="E61">
-        <v>1.665299999999999</v>
+        <v>1.752</v>
       </c>
       <c r="F61">
-        <v>5.1153</v>
+        <v>5.202</v>
       </c>
       <c r="G61">
         <v>0.989</v>
@@ -6277,28 +6277,28 @@
         <v>1.440408163265306</v>
       </c>
       <c r="M61">
-        <v>0.28287609</v>
+        <v>0.2876706</v>
       </c>
       <c r="N61">
-        <v>1.157532073265306</v>
+        <v>1.152737563265306</v>
       </c>
       <c r="O61">
-        <v>0.3472596219795918</v>
+        <v>0.3458212689795918</v>
       </c>
       <c r="P61">
-        <v>0.8102724512857142</v>
+        <v>0.8069162942857142</v>
       </c>
       <c r="Q61">
-        <v>0.8902724512857143</v>
+        <v>0.8869162942857143</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.2918823175659263</v>
+        <v>0.2971149306368907</v>
       </c>
       <c r="T61">
-        <v>1.715794822991825</v>
+        <v>1.752278917040861</v>
       </c>
       <c r="U61">
         <v>0.0553</v>
@@ -6315,7 +6315,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>5.092011004766455</v>
+        <v>5.007144154687014</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6323,22 +6323,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1420719722547563</v>
+        <v>0.1416332943074828</v>
       </c>
       <c r="C62">
-        <v>5.668742878355774</v>
+        <v>5.62425211339622</v>
       </c>
       <c r="D62">
-        <v>9.881742878355773</v>
+        <v>9.923952113396219</v>
       </c>
       <c r="E62">
-        <v>1.752</v>
+        <v>1.838699999999999</v>
       </c>
       <c r="F62">
-        <v>5.202</v>
+        <v>5.2887</v>
       </c>
       <c r="G62">
         <v>0.989</v>
@@ -6359,28 +6359,28 @@
         <v>1.440408163265306</v>
       </c>
       <c r="M62">
-        <v>0.2876706</v>
+        <v>0.29246511</v>
       </c>
       <c r="N62">
-        <v>1.152737563265306</v>
+        <v>1.147943053265306</v>
       </c>
       <c r="O62">
-        <v>0.3458212689795918</v>
+        <v>0.3443829159795918</v>
       </c>
       <c r="P62">
-        <v>0.8069162942857142</v>
+        <v>0.8035601372857143</v>
       </c>
       <c r="Q62">
-        <v>0.8869162942857143</v>
+        <v>0.8835601372857144</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.2971149306368907</v>
+        <v>0.3026158828396994</v>
       </c>
       <c r="T62">
-        <v>1.752278917040861</v>
+        <v>1.7906339902719</v>
       </c>
       <c r="U62">
         <v>0.0553</v>
@@ -6397,7 +6397,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>5.007144154687014</v>
+        <v>4.925059824282309</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6405,22 +6405,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1416332943074828</v>
+        <v>0.1411946163602093</v>
       </c>
       <c r="C63">
-        <v>5.62425211339622</v>
+        <v>5.580123483388845</v>
       </c>
       <c r="D63">
-        <v>9.923952113396219</v>
+        <v>9.966523483388844</v>
       </c>
       <c r="E63">
-        <v>1.838699999999999</v>
+        <v>1.9254</v>
       </c>
       <c r="F63">
-        <v>5.2887</v>
+        <v>5.3754</v>
       </c>
       <c r="G63">
         <v>0.989</v>
@@ -6441,28 +6441,28 @@
         <v>1.440408163265306</v>
       </c>
       <c r="M63">
-        <v>0.29246511</v>
+        <v>0.29725962</v>
       </c>
       <c r="N63">
-        <v>1.147943053265306</v>
+        <v>1.143148543265306</v>
       </c>
       <c r="O63">
-        <v>0.3443829159795918</v>
+        <v>0.3429445629795918</v>
       </c>
       <c r="P63">
-        <v>0.8035601372857143</v>
+        <v>0.8002039802857144</v>
       </c>
       <c r="Q63">
-        <v>0.8835601372857144</v>
+        <v>0.8802039802857144</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.3026158828396994</v>
+        <v>0.308406358842656</v>
       </c>
       <c r="T63">
-        <v>1.7906339902719</v>
+        <v>1.831007751567729</v>
       </c>
       <c r="U63">
         <v>0.0553</v>
@@ -6479,7 +6479,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>4.925059824282309</v>
+        <v>4.845623375503562</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6487,22 +6487,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1411946163602093</v>
+        <v>0.1407559384129358</v>
       </c>
       <c r="C64">
-        <v>5.580123483388845</v>
+        <v>5.536361668827628</v>
       </c>
       <c r="D64">
-        <v>9.966523483388844</v>
+        <v>10.00946166882763</v>
       </c>
       <c r="E64">
-        <v>1.9254</v>
+        <v>2.0121</v>
       </c>
       <c r="F64">
-        <v>5.3754</v>
+        <v>5.4621</v>
       </c>
       <c r="G64">
         <v>0.989</v>
@@ -6523,28 +6523,28 @@
         <v>1.440408163265306</v>
       </c>
       <c r="M64">
-        <v>0.29725962</v>
+        <v>0.30205413</v>
       </c>
       <c r="N64">
-        <v>1.143148543265306</v>
+        <v>1.138354033265306</v>
       </c>
       <c r="O64">
-        <v>0.3429445629795918</v>
+        <v>0.3415062099795919</v>
       </c>
       <c r="P64">
-        <v>0.8002039802857144</v>
+        <v>0.7968478232857144</v>
       </c>
       <c r="Q64">
-        <v>0.8802039802857144</v>
+        <v>0.8768478232857144</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.308406358842656</v>
+        <v>0.3145098335484751</v>
       </c>
       <c r="T64">
-        <v>1.831007751567729</v>
+        <v>1.87356387833901</v>
       </c>
       <c r="U64">
         <v>0.0553</v>
@@ -6561,7 +6561,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>4.845623375503562</v>
+        <v>4.768708718749537</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6569,22 +6569,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1407559384129358</v>
+        <v>0.1403172604656623</v>
       </c>
       <c r="C65">
-        <v>5.536361668827628</v>
+        <v>5.492971431214348</v>
       </c>
       <c r="D65">
-        <v>10.00946166882763</v>
+        <v>10.05277143121435</v>
       </c>
       <c r="E65">
-        <v>2.0121</v>
+        <v>2.0988</v>
       </c>
       <c r="F65">
-        <v>5.4621</v>
+        <v>5.5488</v>
       </c>
       <c r="G65">
         <v>0.989</v>
@@ -6605,28 +6605,28 @@
         <v>1.440408163265306</v>
       </c>
       <c r="M65">
-        <v>0.30205413</v>
+        <v>0.30684864</v>
       </c>
       <c r="N65">
-        <v>1.138354033265306</v>
+        <v>1.133559523265306</v>
       </c>
       <c r="O65">
-        <v>0.3415062099795919</v>
+        <v>0.3400678569795919</v>
       </c>
       <c r="P65">
-        <v>0.7968478232857144</v>
+        <v>0.7934916662857143</v>
       </c>
       <c r="Q65">
-        <v>0.8768478232857144</v>
+        <v>0.8734916662857144</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.3145098335484751</v>
+        <v>0.3209523901823952</v>
       </c>
       <c r="T65">
-        <v>1.87356387833901</v>
+        <v>1.918484234375361</v>
       </c>
       <c r="U65">
         <v>0.0553</v>
@@ -6643,7 +6643,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>4.768708718749537</v>
+        <v>4.694197645019075</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6651,22 +6651,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1403172604656623</v>
+        <v>0.1398785825183888</v>
       </c>
       <c r="C66">
-        <v>5.492971431214348</v>
+        <v>5.449957614818725</v>
       </c>
       <c r="D66">
-        <v>10.05277143121435</v>
+        <v>10.09645761481872</v>
       </c>
       <c r="E66">
-        <v>2.0988</v>
+        <v>2.1855</v>
       </c>
       <c r="F66">
-        <v>5.5488</v>
+        <v>5.6355</v>
       </c>
       <c r="G66">
         <v>0.989</v>
@@ -6687,28 +6687,28 @@
         <v>1.440408163265306</v>
       </c>
       <c r="M66">
-        <v>0.30684864</v>
+        <v>0.31164315</v>
       </c>
       <c r="N66">
-        <v>1.133559523265306</v>
+        <v>1.128765013265306</v>
       </c>
       <c r="O66">
-        <v>0.3400678569795919</v>
+        <v>0.3386295039795918</v>
       </c>
       <c r="P66">
-        <v>0.7934916662857143</v>
+        <v>0.7901355092857142</v>
       </c>
       <c r="Q66">
-        <v>0.8734916662857144</v>
+        <v>0.8701355092857143</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.3209523901823952</v>
+        <v>0.3277630929096823</v>
       </c>
       <c r="T66">
-        <v>1.918484234375361</v>
+        <v>1.965971467899503</v>
       </c>
       <c r="U66">
         <v>0.0553</v>
@@ -6725,7 +6725,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>4.694197645019075</v>
+        <v>4.621979219711089</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6733,22 +6733,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1398785825183888</v>
+        <v>0.1394399045711153</v>
       </c>
       <c r="C67">
-        <v>5.449957614818725</v>
+        <v>5.407325148484712</v>
       </c>
       <c r="D67">
-        <v>10.09645761481872</v>
+        <v>10.14052514848471</v>
       </c>
       <c r="E67">
-        <v>2.1855</v>
+        <v>2.2722</v>
       </c>
       <c r="F67">
-        <v>5.6355</v>
+        <v>5.7222</v>
       </c>
       <c r="G67">
         <v>0.989</v>
@@ -6769,28 +6769,28 @@
         <v>1.440408163265306</v>
       </c>
       <c r="M67">
-        <v>0.31164315</v>
+        <v>0.31643766</v>
       </c>
       <c r="N67">
-        <v>1.128765013265306</v>
+        <v>1.123970503265306</v>
       </c>
       <c r="O67">
-        <v>0.3386295039795918</v>
+        <v>0.3371911509795918</v>
       </c>
       <c r="P67">
-        <v>0.7901355092857142</v>
+        <v>0.7867793522857143</v>
       </c>
       <c r="Q67">
-        <v>0.8701355092857143</v>
+        <v>0.8667793522857143</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.3277630929096823</v>
+        <v>0.3349744252091626</v>
       </c>
       <c r="T67">
-        <v>1.965971467899503</v>
+        <v>2.016252068101537</v>
       </c>
       <c r="U67">
         <v>0.0553</v>
@@ -6807,7 +6807,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>4.621979219711089</v>
+        <v>4.551949231533649</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6815,22 +6815,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1394399045711153</v>
+        <v>0.1401737266238418</v>
       </c>
       <c r="C68">
-        <v>5.407325148484712</v>
+        <v>5.247123722144816</v>
       </c>
       <c r="D68">
-        <v>10.14052514848471</v>
+        <v>10.06702372214482</v>
       </c>
       <c r="E68">
-        <v>2.2722</v>
+        <v>2.3589</v>
       </c>
       <c r="F68">
-        <v>5.7222</v>
+        <v>5.8089</v>
       </c>
       <c r="G68">
         <v>0.989</v>
@@ -6851,45 +6851,45 @@
         <v>1.440408163265306</v>
       </c>
       <c r="M68">
-        <v>0.31643766</v>
+        <v>0.3357544200000001</v>
       </c>
       <c r="N68">
-        <v>1.123970503265306</v>
+        <v>1.104653743265306</v>
       </c>
       <c r="O68">
-        <v>0.3371911509795918</v>
+        <v>0.3313961229795918</v>
       </c>
       <c r="P68">
-        <v>0.7867793522857143</v>
+        <v>0.7732576202857142</v>
       </c>
       <c r="Q68">
-        <v>0.8667793522857143</v>
+        <v>0.8532576202857143</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.3349744252091626</v>
+        <v>0.3426228079510358</v>
       </c>
       <c r="T68">
-        <v>2.016252068101537</v>
+        <v>2.069579977406724</v>
       </c>
       <c r="U68">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V68">
         <v>0.3</v>
       </c>
       <c r="W68">
-        <v>0.03871</v>
+        <v>0.04046</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y68">
-        <v>4.551949231533649</v>
+        <v>4.290064634935575</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6897,22 +6897,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1401737266238418</v>
+        <v>0.1397525486765683</v>
       </c>
       <c r="C69">
-        <v>5.247123722144816</v>
+        <v>5.202479123389155</v>
       </c>
       <c r="D69">
-        <v>10.06702372214482</v>
+        <v>10.10907912338915</v>
       </c>
       <c r="E69">
-        <v>2.3589</v>
+        <v>2.4456</v>
       </c>
       <c r="F69">
-        <v>5.8089</v>
+        <v>5.8956</v>
       </c>
       <c r="G69">
         <v>0.989</v>
@@ -6933,28 +6933,28 @@
         <v>1.440408163265306</v>
       </c>
       <c r="M69">
-        <v>0.3357544200000001</v>
+        <v>0.34076568</v>
       </c>
       <c r="N69">
-        <v>1.104653743265306</v>
+        <v>1.099642483265306</v>
       </c>
       <c r="O69">
-        <v>0.3313961229795918</v>
+        <v>0.3298927449795918</v>
       </c>
       <c r="P69">
-        <v>0.7732576202857142</v>
+        <v>0.7697497382857141</v>
       </c>
       <c r="Q69">
-        <v>0.8532576202857143</v>
+        <v>0.8497497382857142</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.3426228079510358</v>
+        <v>0.350749214614276</v>
       </c>
       <c r="T69">
-        <v>2.069579977406724</v>
+        <v>2.126240881043485</v>
       </c>
       <c r="U69">
         <v>0.0578</v>
@@ -6971,7 +6971,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>4.290064634935575</v>
+        <v>4.2269754491277</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6979,22 +6979,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1397525486765683</v>
+        <v>0.1393313707292948</v>
       </c>
       <c r="C70">
-        <v>5.202479123389155</v>
+        <v>5.158187374980189</v>
       </c>
       <c r="D70">
-        <v>10.10907912338915</v>
+        <v>10.15148737498019</v>
       </c>
       <c r="E70">
-        <v>2.4456</v>
+        <v>2.5323</v>
       </c>
       <c r="F70">
-        <v>5.8956</v>
+        <v>5.9823</v>
       </c>
       <c r="G70">
         <v>0.989</v>
@@ -7015,28 +7015,28 @@
         <v>1.440408163265306</v>
       </c>
       <c r="M70">
-        <v>0.34076568</v>
+        <v>0.34577694</v>
       </c>
       <c r="N70">
-        <v>1.099642483265306</v>
+        <v>1.094631223265306</v>
       </c>
       <c r="O70">
-        <v>0.3298927449795918</v>
+        <v>0.3283893669795918</v>
       </c>
       <c r="P70">
-        <v>0.7697497382857141</v>
+        <v>0.7662418562857142</v>
       </c>
       <c r="Q70">
-        <v>0.8497497382857142</v>
+        <v>0.8462418562857142</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.350749214614276</v>
+        <v>0.3593999055783704</v>
       </c>
       <c r="T70">
-        <v>2.126240881043485</v>
+        <v>2.18655732685036</v>
       </c>
       <c r="U70">
         <v>0.0578</v>
@@ -7053,7 +7053,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>4.2269754491277</v>
+        <v>4.165714935372225</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7061,22 +7061,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1393313707292948</v>
+        <v>0.1389101927820213</v>
       </c>
       <c r="C71">
-        <v>5.158187374980189</v>
+        <v>5.1142529363166</v>
       </c>
       <c r="D71">
-        <v>10.15148737498019</v>
+        <v>10.1942529363166</v>
       </c>
       <c r="E71">
-        <v>2.5323</v>
+        <v>2.619000000000001</v>
       </c>
       <c r="F71">
-        <v>5.9823</v>
+        <v>6.069000000000001</v>
       </c>
       <c r="G71">
         <v>0.989</v>
@@ -7097,28 +7097,28 @@
         <v>1.440408163265306</v>
       </c>
       <c r="M71">
-        <v>0.34577694</v>
+        <v>0.3507882</v>
       </c>
       <c r="N71">
-        <v>1.094631223265306</v>
+        <v>1.089619963265306</v>
       </c>
       <c r="O71">
-        <v>0.3283893669795918</v>
+        <v>0.3268859889795918</v>
       </c>
       <c r="P71">
-        <v>0.7662418562857142</v>
+        <v>0.7627339742857142</v>
       </c>
       <c r="Q71">
-        <v>0.8462418562857142</v>
+        <v>0.8427339742857143</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.3593999055783704</v>
+        <v>0.3686273092734044</v>
       </c>
       <c r="T71">
-        <v>2.18655732685036</v>
+        <v>2.250894869044359</v>
       </c>
       <c r="U71">
         <v>0.0578</v>
@@ -7135,7 +7135,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>4.165714935372225</v>
+        <v>4.106204722009766</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7143,22 +7143,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1389101927820213</v>
+        <v>0.1384890148347478</v>
       </c>
       <c r="C72">
-        <v>5.1142529363166</v>
+        <v>5.070680342260105</v>
       </c>
       <c r="D72">
-        <v>10.1942529363166</v>
+        <v>10.2373803422601</v>
       </c>
       <c r="E72">
-        <v>2.619000000000001</v>
+        <v>2.7057</v>
       </c>
       <c r="F72">
-        <v>6.069000000000001</v>
+        <v>6.1557</v>
       </c>
       <c r="G72">
         <v>0.989</v>
@@ -7179,28 +7179,28 @@
         <v>1.440408163265306</v>
       </c>
       <c r="M72">
-        <v>0.3507882</v>
+        <v>0.3557994600000001</v>
       </c>
       <c r="N72">
-        <v>1.089619963265306</v>
+        <v>1.084608703265306</v>
       </c>
       <c r="O72">
-        <v>0.3268859889795918</v>
+        <v>0.3253826109795918</v>
       </c>
       <c r="P72">
-        <v>0.7627339742857142</v>
+        <v>0.7592260922857141</v>
       </c>
       <c r="Q72">
-        <v>0.8427339742857143</v>
+        <v>0.8392260922857142</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.3686273092734044</v>
+        <v>0.3784910856370615</v>
       </c>
       <c r="T72">
-        <v>2.250894869044359</v>
+        <v>2.319669483113807</v>
       </c>
       <c r="U72">
         <v>0.0578</v>
@@ -7217,7 +7217,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>4.106204722009766</v>
+        <v>4.048370852685684</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7225,22 +7225,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1384890148347478</v>
+        <v>0.1398318368874743</v>
       </c>
       <c r="C73">
-        <v>5.070680342260106</v>
+        <v>4.847735221558802</v>
       </c>
       <c r="D73">
-        <v>10.2373803422601</v>
+        <v>10.1011352215588</v>
       </c>
       <c r="E73">
-        <v>2.705699999999999</v>
+        <v>2.7924</v>
       </c>
       <c r="F73">
-        <v>6.1557</v>
+        <v>6.2424</v>
       </c>
       <c r="G73">
         <v>0.989</v>
@@ -7261,45 +7261,45 @@
         <v>1.440408163265306</v>
       </c>
       <c r="M73">
-        <v>0.35579946</v>
+        <v>0.38265912</v>
       </c>
       <c r="N73">
-        <v>1.084608703265306</v>
+        <v>1.057749043265306</v>
       </c>
       <c r="O73">
-        <v>0.3253826109795918</v>
+        <v>0.3173247129795918</v>
       </c>
       <c r="P73">
-        <v>0.7592260922857141</v>
+        <v>0.7404243302857143</v>
       </c>
       <c r="Q73">
-        <v>0.8392260922857142</v>
+        <v>0.8204243302857144</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.3784910856370614</v>
+        <v>0.3890594174552653</v>
       </c>
       <c r="T73">
-        <v>2.319669483113806</v>
+        <v>2.393356569616786</v>
       </c>
       <c r="U73">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V73">
         <v>0.3</v>
       </c>
       <c r="W73">
-        <v>0.04046</v>
+        <v>0.04291</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y73">
-        <v>4.048370852685684</v>
+        <v>3.764207065717671</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7307,22 +7307,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1398318368874743</v>
+        <v>0.1394351589402008</v>
       </c>
       <c r="C74">
-        <v>4.847735221558802</v>
+        <v>4.800903975700886</v>
       </c>
       <c r="D74">
-        <v>10.1011352215588</v>
+        <v>10.14100397570088</v>
       </c>
       <c r="E74">
-        <v>2.7924</v>
+        <v>2.879099999999999</v>
       </c>
       <c r="F74">
-        <v>6.2424</v>
+        <v>6.3291</v>
       </c>
       <c r="G74">
         <v>0.989</v>
@@ -7343,28 +7343,28 @@
         <v>1.440408163265306</v>
       </c>
       <c r="M74">
-        <v>0.38265912</v>
+        <v>0.38797383</v>
       </c>
       <c r="N74">
-        <v>1.057749043265306</v>
+        <v>1.052434333265306</v>
       </c>
       <c r="O74">
-        <v>0.3173247129795918</v>
+        <v>0.3157302999795918</v>
       </c>
       <c r="P74">
-        <v>0.7404243302857143</v>
+        <v>0.7367040332857142</v>
       </c>
       <c r="Q74">
-        <v>0.8204243302857144</v>
+        <v>0.8167040332857143</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.3890594174552653</v>
+        <v>0.4004105886674104</v>
       </c>
       <c r="T74">
-        <v>2.393356569616786</v>
+        <v>2.472501958823691</v>
       </c>
       <c r="U74">
         <v>0.0613</v>
@@ -7381,7 +7381,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>3.764207065717671</v>
+        <v>3.712642585365374</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7389,22 +7389,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1394351589402008</v>
+        <v>0.1390384809929273</v>
       </c>
       <c r="C75">
-        <v>4.800903975700886</v>
+        <v>4.754388697531929</v>
       </c>
       <c r="D75">
-        <v>10.14100397570088</v>
+        <v>10.18118869753193</v>
       </c>
       <c r="E75">
-        <v>2.879099999999999</v>
+        <v>2.9658</v>
       </c>
       <c r="F75">
-        <v>6.3291</v>
+        <v>6.4158</v>
       </c>
       <c r="G75">
         <v>0.989</v>
@@ -7425,28 +7425,28 @@
         <v>1.440408163265306</v>
       </c>
       <c r="M75">
-        <v>0.38797383</v>
+        <v>0.39328854</v>
       </c>
       <c r="N75">
-        <v>1.052434333265306</v>
+        <v>1.047119623265306</v>
       </c>
       <c r="O75">
-        <v>0.3157302999795918</v>
+        <v>0.3141358869795918</v>
       </c>
       <c r="P75">
-        <v>0.7367040332857142</v>
+        <v>0.7329837362857141</v>
       </c>
       <c r="Q75">
-        <v>0.8167040332857143</v>
+        <v>0.8129837362857142</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.4004105886674104</v>
+        <v>0.4126349268958742</v>
       </c>
       <c r="T75">
-        <v>2.472501958823691</v>
+        <v>2.557735454892665</v>
       </c>
       <c r="U75">
         <v>0.0613</v>
@@ -7463,7 +7463,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>3.712642585365374</v>
+        <v>3.662471739617193</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7471,22 +7471,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1390384809929273</v>
+        <v>0.1386418030456538</v>
       </c>
       <c r="C76">
-        <v>4.754388697531929</v>
+        <v>4.708193158154062</v>
       </c>
       <c r="D76">
-        <v>10.18118869753193</v>
+        <v>10.22169315815406</v>
       </c>
       <c r="E76">
-        <v>2.9658</v>
+        <v>3.052499999999999</v>
       </c>
       <c r="F76">
-        <v>6.4158</v>
+        <v>6.5025</v>
       </c>
       <c r="G76">
         <v>0.989</v>
@@ -7507,28 +7507,28 @@
         <v>1.440408163265306</v>
       </c>
       <c r="M76">
-        <v>0.39328854</v>
+        <v>0.39860325</v>
       </c>
       <c r="N76">
-        <v>1.047119623265306</v>
+        <v>1.041804913265306</v>
       </c>
       <c r="O76">
-        <v>0.3141358869795918</v>
+        <v>0.3125414739795918</v>
       </c>
       <c r="P76">
-        <v>0.7329837362857141</v>
+        <v>0.7292634392857142</v>
       </c>
       <c r="Q76">
-        <v>0.8129837362857142</v>
+        <v>0.8092634392857143</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.4126349268958742</v>
+        <v>0.4258372121826152</v>
       </c>
       <c r="T76">
-        <v>2.557735454892665</v>
+        <v>2.649787630647156</v>
       </c>
       <c r="U76">
         <v>0.0613</v>
@@ -7545,7 +7545,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>3.662471739617193</v>
+        <v>3.613638783088964</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7553,22 +7553,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1386418030456538</v>
+        <v>0.1382451250983803</v>
       </c>
       <c r="C77">
-        <v>4.708193158154062</v>
+        <v>4.662321188920371</v>
       </c>
       <c r="D77">
-        <v>10.22169315815406</v>
+        <v>10.26252118892037</v>
       </c>
       <c r="E77">
-        <v>3.052499999999999</v>
+        <v>3.1392</v>
       </c>
       <c r="F77">
-        <v>6.5025</v>
+        <v>6.5892</v>
       </c>
       <c r="G77">
         <v>0.989</v>
@@ -7589,28 +7589,28 @@
         <v>1.440408163265306</v>
       </c>
       <c r="M77">
-        <v>0.39860325</v>
+        <v>0.40391796</v>
       </c>
       <c r="N77">
-        <v>1.041804913265306</v>
+        <v>1.036490203265306</v>
       </c>
       <c r="O77">
-        <v>0.3125414739795918</v>
+        <v>0.3109470609795918</v>
       </c>
       <c r="P77">
-        <v>0.7292634392857142</v>
+        <v>0.7255431422857143</v>
       </c>
       <c r="Q77">
-        <v>0.8092634392857143</v>
+        <v>0.8055431422857143</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.4258372121826152</v>
+        <v>0.440139687909918</v>
       </c>
       <c r="T77">
-        <v>2.649787630647156</v>
+        <v>2.749510821047856</v>
       </c>
       <c r="U77">
         <v>0.0613</v>
@@ -7627,7 +7627,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>3.613638783088964</v>
+        <v>3.566090904364109</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7635,22 +7635,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1382451250983803</v>
+        <v>0.1378484471511068</v>
       </c>
       <c r="C78">
-        <v>4.662321188920371</v>
+        <v>4.616776682643</v>
       </c>
       <c r="D78">
-        <v>10.26252118892037</v>
+        <v>10.303676682643</v>
       </c>
       <c r="E78">
-        <v>3.1392</v>
+        <v>3.2259</v>
       </c>
       <c r="F78">
-        <v>6.5892</v>
+        <v>6.6759</v>
       </c>
       <c r="G78">
         <v>0.989</v>
@@ -7671,28 +7671,28 @@
         <v>1.440408163265306</v>
       </c>
       <c r="M78">
-        <v>0.40391796</v>
+        <v>0.40923267</v>
       </c>
       <c r="N78">
-        <v>1.036490203265306</v>
+        <v>1.031175493265306</v>
       </c>
       <c r="O78">
-        <v>0.3109470609795918</v>
+        <v>0.3093526479795918</v>
       </c>
       <c r="P78">
-        <v>0.7255431422857143</v>
+        <v>0.7218228452857143</v>
       </c>
       <c r="Q78">
-        <v>0.8055431422857143</v>
+        <v>0.8018228452857143</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.440139687909918</v>
+        <v>0.4556858571787253</v>
       </c>
       <c r="T78">
-        <v>2.749510821047856</v>
+        <v>2.857905593222529</v>
       </c>
       <c r="U78">
         <v>0.0613</v>
@@ -7709,7 +7709,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>3.566090904364109</v>
+        <v>3.519778035476264</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7717,22 +7717,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1378484471511068</v>
+        <v>0.1389805692038333</v>
       </c>
       <c r="C79">
-        <v>4.616776682643</v>
+        <v>4.413482000119182</v>
       </c>
       <c r="D79">
-        <v>10.303676682643</v>
+        <v>10.18708200011918</v>
       </c>
       <c r="E79">
-        <v>3.2259</v>
+        <v>3.3126</v>
       </c>
       <c r="F79">
-        <v>6.6759</v>
+        <v>6.7626</v>
       </c>
       <c r="G79">
         <v>0.989</v>
@@ -7753,45 +7753,45 @@
         <v>1.440408163265306</v>
       </c>
       <c r="M79">
-        <v>0.40923267</v>
+        <v>0.43348266</v>
       </c>
       <c r="N79">
-        <v>1.031175493265306</v>
+        <v>1.006925503265306</v>
       </c>
       <c r="O79">
-        <v>0.3093526479795918</v>
+        <v>0.3020776509795918</v>
       </c>
       <c r="P79">
-        <v>0.7218228452857143</v>
+        <v>0.7048478522857143</v>
       </c>
       <c r="Q79">
-        <v>0.8018228452857143</v>
+        <v>0.7848478522857144</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.4556858571787253</v>
+        <v>0.4726453145628787</v>
       </c>
       <c r="T79">
-        <v>2.857905593222529</v>
+        <v>2.9761544355949</v>
       </c>
       <c r="U79">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V79">
         <v>0.3</v>
       </c>
       <c r="W79">
-        <v>0.04291</v>
+        <v>0.04487</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y79">
-        <v>3.519778035476264</v>
+        <v>3.322873776001343</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7799,22 +7799,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1389805692038333</v>
+        <v>0.1386034912565598</v>
       </c>
       <c r="C80">
-        <v>4.413482000119182</v>
+        <v>4.36532221657533</v>
       </c>
       <c r="D80">
-        <v>10.18708200011918</v>
+        <v>10.22562221657533</v>
       </c>
       <c r="E80">
-        <v>3.3126</v>
+        <v>3.3993</v>
       </c>
       <c r="F80">
-        <v>6.7626</v>
+        <v>6.8493</v>
       </c>
       <c r="G80">
         <v>0.989</v>
@@ -7835,28 +7835,28 @@
         <v>1.440408163265306</v>
       </c>
       <c r="M80">
-        <v>0.43348266</v>
+        <v>0.43904013</v>
       </c>
       <c r="N80">
-        <v>1.006925503265306</v>
+        <v>1.001368033265306</v>
       </c>
       <c r="O80">
-        <v>0.3020776509795918</v>
+        <v>0.3004104099795918</v>
       </c>
       <c r="P80">
-        <v>0.7048478522857143</v>
+        <v>0.7009576232857142</v>
       </c>
       <c r="Q80">
-        <v>0.7848478522857144</v>
+        <v>0.7809576232857143</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.4726453145628787</v>
+        <v>0.4912199583645706</v>
       </c>
       <c r="T80">
-        <v>2.9761544355949</v>
+        <v>3.105665072478926</v>
       </c>
       <c r="U80">
         <v>0.0641</v>
@@ -7873,7 +7873,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>3.322873776001343</v>
+        <v>3.280812082634237</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7881,22 +7881,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1386034912565598</v>
+        <v>0.1382264133092863</v>
       </c>
       <c r="C81">
-        <v>4.36532221657533</v>
+        <v>4.317455154550721</v>
       </c>
       <c r="D81">
-        <v>10.22562221657533</v>
+        <v>10.26445515455072</v>
       </c>
       <c r="E81">
-        <v>3.3993</v>
+        <v>3.486</v>
       </c>
       <c r="F81">
-        <v>6.8493</v>
+        <v>6.936</v>
       </c>
       <c r="G81">
         <v>0.989</v>
@@ -7917,28 +7917,28 @@
         <v>1.440408163265306</v>
       </c>
       <c r="M81">
-        <v>0.43904013</v>
+        <v>0.4445976</v>
       </c>
       <c r="N81">
-        <v>1.001368033265306</v>
+        <v>0.995810563265306</v>
       </c>
       <c r="O81">
-        <v>0.3004104099795918</v>
+        <v>0.2987431689795918</v>
       </c>
       <c r="P81">
-        <v>0.7009576232857142</v>
+        <v>0.6970673942857142</v>
       </c>
       <c r="Q81">
-        <v>0.7809576232857143</v>
+        <v>0.7770673942857143</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.4912199583645706</v>
+        <v>0.5116520665464316</v>
       </c>
       <c r="T81">
-        <v>3.105665072478926</v>
+        <v>3.248126773051354</v>
       </c>
       <c r="U81">
         <v>0.0641</v>
@@ -7955,7 +7955,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>3.280812082634237</v>
+        <v>3.239801931601308</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7963,22 +7963,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1382264133092863</v>
+        <v>0.1378493353620128</v>
       </c>
       <c r="C82">
-        <v>4.317455154550721</v>
+        <v>4.269884161685992</v>
       </c>
       <c r="D82">
-        <v>10.26445515455072</v>
+        <v>10.30358416168599</v>
       </c>
       <c r="E82">
-        <v>3.486</v>
+        <v>3.5727</v>
       </c>
       <c r="F82">
-        <v>6.936</v>
+        <v>7.0227</v>
       </c>
       <c r="G82">
         <v>0.989</v>
@@ -7999,28 +7999,28 @@
         <v>1.440408163265306</v>
       </c>
       <c r="M82">
-        <v>0.4445976</v>
+        <v>0.45015507</v>
       </c>
       <c r="N82">
-        <v>0.995810563265306</v>
+        <v>0.990253093265306</v>
       </c>
       <c r="O82">
-        <v>0.2987431689795918</v>
+        <v>0.2970759279795918</v>
       </c>
       <c r="P82">
-        <v>0.6970673942857142</v>
+        <v>0.6931771652857142</v>
       </c>
       <c r="Q82">
-        <v>0.7770673942857143</v>
+        <v>0.7731771652857142</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.5116520665464316</v>
+        <v>0.5342349229579623</v>
       </c>
       <c r="T82">
-        <v>3.248126773051354</v>
+        <v>3.40558444210509</v>
       </c>
       <c r="U82">
         <v>0.0641</v>
@@ -8037,7 +8037,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>3.239801931601308</v>
+        <v>3.199804376890181</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8045,22 +8045,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1378493353620128</v>
+        <v>0.1374722574147393</v>
       </c>
       <c r="C83">
-        <v>4.269884161685992</v>
+        <v>4.222612636863126</v>
       </c>
       <c r="D83">
-        <v>10.30358416168599</v>
+        <v>10.34301263686313</v>
       </c>
       <c r="E83">
-        <v>3.5727</v>
+        <v>3.659400000000001</v>
       </c>
       <c r="F83">
-        <v>7.0227</v>
+        <v>7.109400000000001</v>
       </c>
       <c r="G83">
         <v>0.989</v>
@@ -8081,28 +8081,28 @@
         <v>1.440408163265306</v>
       </c>
       <c r="M83">
-        <v>0.45015507</v>
+        <v>0.4557125400000001</v>
       </c>
       <c r="N83">
-        <v>0.990253093265306</v>
+        <v>0.9846956232653059</v>
       </c>
       <c r="O83">
-        <v>0.2970759279795918</v>
+        <v>0.2954086869795918</v>
       </c>
       <c r="P83">
-        <v>0.6931771652857142</v>
+        <v>0.6892869362857141</v>
       </c>
       <c r="Q83">
-        <v>0.7731771652857142</v>
+        <v>0.7692869362857142</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.5342349229579623</v>
+        <v>0.5593269856374407</v>
       </c>
       <c r="T83">
-        <v>3.40558444210509</v>
+        <v>3.580537407720352</v>
       </c>
       <c r="U83">
         <v>0.0641</v>
@@ -8119,7 +8119,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>3.199804376890181</v>
+        <v>3.160782372293959</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8127,22 +8127,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1374722574147393</v>
+        <v>0.1370951794674658</v>
       </c>
       <c r="C84">
-        <v>4.222612636863126</v>
+        <v>4.175644031189633</v>
       </c>
       <c r="D84">
-        <v>10.34301263686313</v>
+        <v>10.38274403118963</v>
       </c>
       <c r="E84">
-        <v>3.659400000000001</v>
+        <v>3.7461</v>
       </c>
       <c r="F84">
-        <v>7.109400000000001</v>
+        <v>7.1961</v>
       </c>
       <c r="G84">
         <v>0.989</v>
@@ -8163,28 +8163,28 @@
         <v>1.440408163265306</v>
       </c>
       <c r="M84">
-        <v>0.4557125400000001</v>
+        <v>0.4612700100000001</v>
       </c>
       <c r="N84">
-        <v>0.9846956232653059</v>
+        <v>0.9791381532653061</v>
       </c>
       <c r="O84">
-        <v>0.2954086869795918</v>
+        <v>0.2937414459795918</v>
       </c>
       <c r="P84">
-        <v>0.6892869362857141</v>
+        <v>0.6853967072857143</v>
       </c>
       <c r="Q84">
-        <v>0.7692869362857142</v>
+        <v>0.7653967072857144</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.5593269856374407</v>
+        <v>0.5873710556909755</v>
       </c>
       <c r="T84">
-        <v>3.580537407720352</v>
+        <v>3.776073075172704</v>
       </c>
       <c r="U84">
         <v>0.0641</v>
@@ -8201,7 +8201,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>3.160782372293959</v>
+        <v>3.122700656965117</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8209,22 +8209,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1370951794674658</v>
+        <v>0.1367181015201923</v>
       </c>
       <c r="C85">
-        <v>4.175644031189633</v>
+        <v>4.128981849005505</v>
       </c>
       <c r="D85">
-        <v>10.38274403118963</v>
+        <v>10.4227818490055</v>
       </c>
       <c r="E85">
-        <v>3.7461</v>
+        <v>3.832800000000001</v>
       </c>
       <c r="F85">
-        <v>7.1961</v>
+        <v>7.282800000000001</v>
       </c>
       <c r="G85">
         <v>0.989</v>
@@ -8245,28 +8245,28 @@
         <v>1.440408163265306</v>
       </c>
       <c r="M85">
-        <v>0.4612700100000001</v>
+        <v>0.4668274800000001</v>
       </c>
       <c r="N85">
-        <v>0.9791381532653061</v>
+        <v>0.973580683265306</v>
       </c>
       <c r="O85">
-        <v>0.2937414459795918</v>
+        <v>0.2920742049795918</v>
       </c>
       <c r="P85">
-        <v>0.6853967072857143</v>
+        <v>0.6815064782857142</v>
       </c>
       <c r="Q85">
-        <v>0.7653967072857144</v>
+        <v>0.7615064782857143</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.5873710556909755</v>
+        <v>0.6189206345012023</v>
       </c>
       <c r="T85">
-        <v>3.776073075172704</v>
+        <v>3.996050701056601</v>
       </c>
       <c r="U85">
         <v>0.0641</v>
@@ -8283,7 +8283,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>3.122700656965117</v>
+        <v>3.085525649144103</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8291,22 +8291,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1367181015201923</v>
+        <v>0.1363410235729188</v>
       </c>
       <c r="C86">
-        <v>4.128981849005505</v>
+        <v>4.08262964891357</v>
       </c>
       <c r="D86">
-        <v>10.4227818490055</v>
+        <v>10.46312964891357</v>
       </c>
       <c r="E86">
-        <v>3.8328</v>
+        <v>3.919499999999999</v>
       </c>
       <c r="F86">
-        <v>7.2828</v>
+        <v>7.369499999999999</v>
       </c>
       <c r="G86">
         <v>0.989</v>
@@ -8327,28 +8327,28 @@
         <v>1.440408163265306</v>
       </c>
       <c r="M86">
-        <v>0.46682748</v>
+        <v>0.47238495</v>
       </c>
       <c r="N86">
-        <v>0.973580683265306</v>
+        <v>0.968023213265306</v>
       </c>
       <c r="O86">
-        <v>0.2920742049795918</v>
+        <v>0.2904069639795918</v>
       </c>
       <c r="P86">
-        <v>0.6815064782857142</v>
+        <v>0.6776162492857143</v>
       </c>
       <c r="Q86">
-        <v>0.7615064782857143</v>
+        <v>0.7576162492857144</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.6189206345012018</v>
+        <v>0.6546768238194586</v>
       </c>
       <c r="T86">
-        <v>3.996050701056598</v>
+        <v>4.245358677058347</v>
       </c>
       <c r="U86">
         <v>0.0641</v>
@@ -8365,7 +8365,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>3.085525649144103</v>
+        <v>3.049225347389467</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8373,22 +8373,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1363410235729188</v>
+        <v>0.1359639456256453</v>
       </c>
       <c r="C87">
-        <v>4.08262964891357</v>
+        <v>4.036591044833842</v>
       </c>
       <c r="D87">
-        <v>10.46312964891357</v>
+        <v>10.50379104483384</v>
       </c>
       <c r="E87">
-        <v>3.919499999999999</v>
+        <v>4.0062</v>
       </c>
       <c r="F87">
-        <v>7.369499999999999</v>
+        <v>7.4562</v>
       </c>
       <c r="G87">
         <v>0.989</v>
@@ -8409,28 +8409,28 @@
         <v>1.440408163265306</v>
       </c>
       <c r="M87">
-        <v>0.47238495</v>
+        <v>0.47794242</v>
       </c>
       <c r="N87">
-        <v>0.968023213265306</v>
+        <v>0.9624657432653061</v>
       </c>
       <c r="O87">
-        <v>0.2904069639795918</v>
+        <v>0.2887397229795918</v>
       </c>
       <c r="P87">
-        <v>0.6776162492857143</v>
+        <v>0.6737260202857143</v>
       </c>
       <c r="Q87">
-        <v>0.7576162492857144</v>
+        <v>0.7537260202857143</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.6546768238194586</v>
+        <v>0.6955410401831807</v>
       </c>
       <c r="T87">
-        <v>4.245358677058347</v>
+        <v>4.530282078203203</v>
       </c>
       <c r="U87">
         <v>0.0641</v>
@@ -8447,7 +8447,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>3.049225347389467</v>
+        <v>3.013769238698892</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8455,22 +8455,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1359639456256453</v>
+        <v>0.1403370676783718</v>
       </c>
       <c r="C88">
-        <v>4.036591044833842</v>
+        <v>3.496907828550871</v>
       </c>
       <c r="D88">
-        <v>10.50379104483384</v>
+        <v>10.05080782855087</v>
       </c>
       <c r="E88">
-        <v>4.0062</v>
+        <v>4.092899999999999</v>
       </c>
       <c r="F88">
-        <v>7.4562</v>
+        <v>7.542899999999999</v>
       </c>
       <c r="G88">
         <v>0.989</v>
@@ -8491,45 +8491,45 @@
         <v>1.440408163265306</v>
       </c>
       <c r="M88">
-        <v>0.47794242</v>
+        <v>0.54233451</v>
       </c>
       <c r="N88">
-        <v>0.9624657432653061</v>
+        <v>0.8980736532653061</v>
       </c>
       <c r="O88">
-        <v>0.2887397229795918</v>
+        <v>0.2694220959795918</v>
       </c>
       <c r="P88">
-        <v>0.6737260202857143</v>
+        <v>0.6286515572857143</v>
       </c>
       <c r="Q88">
-        <v>0.7537260202857143</v>
+        <v>0.7086515572857144</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.6955410401831807</v>
+        <v>0.7426920590643985</v>
       </c>
       <c r="T88">
-        <v>4.530282078203203</v>
+        <v>4.859039848754959</v>
       </c>
       <c r="U88">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V88">
         <v>0.3</v>
       </c>
       <c r="W88">
-        <v>0.04487</v>
+        <v>0.05033</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y88">
-        <v>3.013769238698892</v>
+        <v>2.655940451337508</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8537,22 +8537,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1403370676783718</v>
+        <v>0.1400145897310983</v>
       </c>
       <c r="C89">
-        <v>3.496907828550871</v>
+        <v>3.442272643744849</v>
       </c>
       <c r="D89">
-        <v>10.05080782855087</v>
+        <v>10.08287264374485</v>
       </c>
       <c r="E89">
-        <v>4.092899999999999</v>
+        <v>4.1796</v>
       </c>
       <c r="F89">
-        <v>7.542899999999999</v>
+        <v>7.6296</v>
       </c>
       <c r="G89">
         <v>0.989</v>
@@ -8573,28 +8573,28 @@
         <v>1.440408163265306</v>
       </c>
       <c r="M89">
-        <v>0.54233451</v>
+        <v>0.54856824</v>
       </c>
       <c r="N89">
-        <v>0.8980736532653061</v>
+        <v>0.891839923265306</v>
       </c>
       <c r="O89">
-        <v>0.2694220959795918</v>
+        <v>0.2675519769795918</v>
       </c>
       <c r="P89">
-        <v>0.6286515572857143</v>
+        <v>0.6242879462857143</v>
       </c>
       <c r="Q89">
-        <v>0.7086515572857144</v>
+        <v>0.7042879462857143</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.7426920590643985</v>
+        <v>0.797701581092486</v>
       </c>
       <c r="T89">
-        <v>4.859039848754959</v>
+        <v>5.242590581065342</v>
       </c>
       <c r="U89">
         <v>0.07190000000000001</v>
@@ -8611,7 +8611,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>2.655940451337508</v>
+        <v>2.625759309845036</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8619,22 +8619,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1400145897310983</v>
+        <v>0.1396921117838248</v>
       </c>
       <c r="C90">
-        <v>3.442272643744849</v>
+        <v>3.387842704721068</v>
       </c>
       <c r="D90">
-        <v>10.08287264374485</v>
+        <v>10.11514270472107</v>
       </c>
       <c r="E90">
-        <v>4.1796</v>
+        <v>4.2663</v>
       </c>
       <c r="F90">
-        <v>7.6296</v>
+        <v>7.7163</v>
       </c>
       <c r="G90">
         <v>0.989</v>
@@ -8655,28 +8655,28 @@
         <v>1.440408163265306</v>
       </c>
       <c r="M90">
-        <v>0.54856824</v>
+        <v>0.5548019700000001</v>
       </c>
       <c r="N90">
-        <v>0.891839923265306</v>
+        <v>0.885606193265306</v>
       </c>
       <c r="O90">
-        <v>0.2675519769795918</v>
+        <v>0.2656818579795918</v>
       </c>
       <c r="P90">
-        <v>0.6242879462857143</v>
+        <v>0.6199243352857142</v>
       </c>
       <c r="Q90">
-        <v>0.7042879462857143</v>
+        <v>0.6999243352857143</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.797701581092486</v>
+        <v>0.8627128343984074</v>
       </c>
       <c r="T90">
-        <v>5.242590581065342</v>
+        <v>5.695877810159431</v>
       </c>
       <c r="U90">
         <v>0.07190000000000001</v>
@@ -8693,7 +8693,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>2.625759309845036</v>
+        <v>2.596256396251271</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8701,22 +8701,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1396921117838248</v>
+        <v>0.1393696338365513</v>
       </c>
       <c r="C91">
-        <v>3.387842704721068</v>
+        <v>3.333619988463647</v>
       </c>
       <c r="D91">
-        <v>10.11514270472107</v>
+        <v>10.14761998846365</v>
       </c>
       <c r="E91">
-        <v>4.2663</v>
+        <v>4.353</v>
       </c>
       <c r="F91">
-        <v>7.7163</v>
+        <v>7.803</v>
       </c>
       <c r="G91">
         <v>0.989</v>
@@ -8737,28 +8737,28 @@
         <v>1.440408163265306</v>
       </c>
       <c r="M91">
-        <v>0.5548019700000001</v>
+        <v>0.5610357</v>
       </c>
       <c r="N91">
-        <v>0.885606193265306</v>
+        <v>0.879372463265306</v>
       </c>
       <c r="O91">
-        <v>0.2656818579795918</v>
+        <v>0.2638117389795918</v>
       </c>
       <c r="P91">
-        <v>0.6199243352857142</v>
+        <v>0.6155607242857142</v>
       </c>
       <c r="Q91">
-        <v>0.6999243352857143</v>
+        <v>0.6955607242857142</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.8627128343984074</v>
+        <v>0.9407263383655133</v>
       </c>
       <c r="T91">
-        <v>5.695877810159431</v>
+        <v>6.239822485072337</v>
       </c>
       <c r="U91">
         <v>0.07190000000000001</v>
@@ -8775,7 +8775,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>2.596256396251271</v>
+        <v>2.567409102959591</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8783,22 +8783,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1393696338365513</v>
+        <v>0.1390471558892778</v>
       </c>
       <c r="C92">
-        <v>3.333619988463647</v>
+        <v>3.279606497428975</v>
       </c>
       <c r="D92">
-        <v>10.14761998846365</v>
+        <v>10.18030649742897</v>
       </c>
       <c r="E92">
-        <v>4.353</v>
+        <v>4.4397</v>
       </c>
       <c r="F92">
-        <v>7.803</v>
+        <v>7.8897</v>
       </c>
       <c r="G92">
         <v>0.989</v>
@@ -8819,28 +8819,28 @@
         <v>1.440408163265306</v>
       </c>
       <c r="M92">
-        <v>0.5610357</v>
+        <v>0.5672694300000001</v>
       </c>
       <c r="N92">
-        <v>0.879372463265306</v>
+        <v>0.873138733265306</v>
       </c>
       <c r="O92">
-        <v>0.2638117389795918</v>
+        <v>0.2619416199795918</v>
       </c>
       <c r="P92">
-        <v>0.6155607242857142</v>
+        <v>0.6111971132857141</v>
       </c>
       <c r="Q92">
-        <v>0.6955607242857142</v>
+        <v>0.6911971132857142</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.9407263383655133</v>
+        <v>1.036076176547532</v>
       </c>
       <c r="T92">
-        <v>6.239822485072337</v>
+        <v>6.904643754410334</v>
       </c>
       <c r="U92">
         <v>0.07190000000000001</v>
@@ -8857,7 +8857,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>2.567409102959591</v>
+        <v>2.539195816113881</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8865,22 +8865,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1390471558892778</v>
+        <v>0.1387246779420043</v>
       </c>
       <c r="C93">
-        <v>3.279606497428975</v>
+        <v>3.225804259957268</v>
       </c>
       <c r="D93">
-        <v>10.18030649742897</v>
+        <v>10.21320425995727</v>
       </c>
       <c r="E93">
-        <v>4.4397</v>
+        <v>4.5264</v>
       </c>
       <c r="F93">
-        <v>7.8897</v>
+        <v>7.9764</v>
       </c>
       <c r="G93">
         <v>0.989</v>
@@ -8901,28 +8901,28 @@
         <v>1.440408163265306</v>
       </c>
       <c r="M93">
-        <v>0.5672694300000001</v>
+        <v>0.57350316</v>
       </c>
       <c r="N93">
-        <v>0.873138733265306</v>
+        <v>0.8669050032653061</v>
       </c>
       <c r="O93">
-        <v>0.2619416199795918</v>
+        <v>0.2600715009795918</v>
       </c>
       <c r="P93">
-        <v>0.6111971132857141</v>
+        <v>0.6068335022857143</v>
       </c>
       <c r="Q93">
-        <v>0.6911971132857142</v>
+        <v>0.6868335022857144</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>1.036076176547532</v>
+        <v>1.155263474275055</v>
       </c>
       <c r="T93">
-        <v>6.904643754410334</v>
+        <v>7.735670341082832</v>
       </c>
       <c r="U93">
         <v>0.07190000000000001</v>
@@ -8939,7 +8939,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>2.539195816113881</v>
+        <v>2.511595861590904</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8947,22 +8947,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.1387246779420043</v>
+        <v>0.1409410999947308</v>
       </c>
       <c r="C94">
-        <v>3.225804259957268</v>
+        <v>2.917192847213389</v>
       </c>
       <c r="D94">
-        <v>10.21320425995727</v>
+        <v>9.991292847213389</v>
       </c>
       <c r="E94">
-        <v>4.5264</v>
+        <v>4.6131</v>
       </c>
       <c r="F94">
-        <v>7.9764</v>
+        <v>8.0631</v>
       </c>
       <c r="G94">
         <v>0.989</v>
@@ -8983,45 +8983,45 @@
         <v>1.440408163265306</v>
       </c>
       <c r="M94">
-        <v>0.57350316</v>
+        <v>0.61118298</v>
       </c>
       <c r="N94">
-        <v>0.8669050032653061</v>
+        <v>0.829225183265306</v>
       </c>
       <c r="O94">
-        <v>0.2600715009795918</v>
+        <v>0.2487675549795918</v>
       </c>
       <c r="P94">
-        <v>0.6068335022857143</v>
+        <v>0.5804576282857142</v>
       </c>
       <c r="Q94">
-        <v>0.6868335022857144</v>
+        <v>0.6604576282857143</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>1.155263474275055</v>
+        <v>1.308504285639013</v>
       </c>
       <c r="T94">
-        <v>7.735670341082832</v>
+        <v>8.804133095376041</v>
       </c>
       <c r="U94">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V94">
         <v>0.3</v>
       </c>
       <c r="W94">
-        <v>0.05033</v>
+        <v>0.05306</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y94">
-        <v>2.511595861590904</v>
+        <v>2.356754377003931</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9029,22 +9029,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.1409410999947308</v>
+        <v>0.1406459220474574</v>
       </c>
       <c r="C95">
-        <v>2.917192847213389</v>
+        <v>2.859488259040075</v>
       </c>
       <c r="D95">
-        <v>9.991292847213389</v>
+        <v>10.02028825904008</v>
       </c>
       <c r="E95">
-        <v>4.6131</v>
+        <v>4.699800000000001</v>
       </c>
       <c r="F95">
-        <v>8.0631</v>
+        <v>8.149800000000001</v>
       </c>
       <c r="G95">
         <v>0.989</v>
@@ -9065,28 +9065,28 @@
         <v>1.440408163265306</v>
       </c>
       <c r="M95">
-        <v>0.61118298</v>
+        <v>0.6177548400000001</v>
       </c>
       <c r="N95">
-        <v>0.829225183265306</v>
+        <v>0.8226533232653059</v>
       </c>
       <c r="O95">
-        <v>0.2487675549795918</v>
+        <v>0.2467959969795918</v>
       </c>
       <c r="P95">
-        <v>0.5804576282857142</v>
+        <v>0.5758573262857142</v>
       </c>
       <c r="Q95">
-        <v>0.6604576282857143</v>
+        <v>0.6558573262857142</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>1.308504285639013</v>
+        <v>1.512825367457624</v>
       </c>
       <c r="T95">
-        <v>8.804133095376041</v>
+        <v>10.22875010110032</v>
       </c>
       <c r="U95">
         <v>0.07580000000000001</v>
@@ -9103,7 +9103,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>2.356754377003931</v>
+        <v>2.33168252192942</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9111,22 +9111,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1406459220474574</v>
+        <v>0.1403507441001838</v>
       </c>
       <c r="C96">
-        <v>2.859488259040075</v>
+        <v>2.801952454003883</v>
       </c>
       <c r="D96">
-        <v>10.02028825904008</v>
+        <v>10.04945245400388</v>
       </c>
       <c r="E96">
-        <v>4.699800000000001</v>
+        <v>4.786500000000001</v>
       </c>
       <c r="F96">
-        <v>8.149800000000001</v>
+        <v>8.236500000000001</v>
       </c>
       <c r="G96">
         <v>0.989</v>
@@ -9147,28 +9147,28 @@
         <v>1.440408163265306</v>
       </c>
       <c r="M96">
-        <v>0.6177548400000001</v>
+        <v>0.6243267000000001</v>
       </c>
       <c r="N96">
-        <v>0.8226533232653059</v>
+        <v>0.816081463265306</v>
       </c>
       <c r="O96">
-        <v>0.2467959969795918</v>
+        <v>0.2448244389795918</v>
       </c>
       <c r="P96">
-        <v>0.5758573262857142</v>
+        <v>0.5712570242857142</v>
       </c>
       <c r="Q96">
-        <v>0.6558573262857142</v>
+        <v>0.6512570242857143</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.512825367457624</v>
+        <v>1.798874882003679</v>
       </c>
       <c r="T96">
-        <v>10.22875010110032</v>
+        <v>12.22321390911432</v>
       </c>
       <c r="U96">
         <v>0.07580000000000001</v>
@@ -9185,7 +9185,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>2.33168252192942</v>
+        <v>2.307138495382795</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9193,22 +9193,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.1403507441001838</v>
+        <v>0.1400555661529103</v>
       </c>
       <c r="C97">
-        <v>2.801952454003883</v>
+        <v>2.744586910143997</v>
       </c>
       <c r="D97">
-        <v>10.04945245400388</v>
+        <v>10.078786910144</v>
       </c>
       <c r="E97">
-        <v>4.786500000000001</v>
+        <v>4.8732</v>
       </c>
       <c r="F97">
-        <v>8.236500000000001</v>
+        <v>8.3232</v>
       </c>
       <c r="G97">
         <v>0.989</v>
@@ -9229,28 +9229,28 @@
         <v>1.440408163265306</v>
       </c>
       <c r="M97">
-        <v>0.6243267000000001</v>
+        <v>0.63089856</v>
       </c>
       <c r="N97">
-        <v>0.816081463265306</v>
+        <v>0.8095096032653061</v>
       </c>
       <c r="O97">
-        <v>0.2448244389795918</v>
+        <v>0.2428528809795918</v>
       </c>
       <c r="P97">
-        <v>0.5712570242857142</v>
+        <v>0.5666567222857143</v>
       </c>
       <c r="Q97">
-        <v>0.6512570242857143</v>
+        <v>0.6466567222857144</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.798874882003679</v>
+        <v>2.227949153822762</v>
       </c>
       <c r="T97">
-        <v>12.22321390911432</v>
+        <v>15.21490962113531</v>
       </c>
       <c r="U97">
         <v>0.07580000000000001</v>
@@ -9267,7 +9267,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>2.307138495382795</v>
+        <v>2.283105802722558</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9275,22 +9275,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.1400555661529103</v>
+        <v>0.1397603882056369</v>
       </c>
       <c r="C98">
-        <v>2.744586910143997</v>
+        <v>2.687393122807773</v>
       </c>
       <c r="D98">
-        <v>10.078786910144</v>
+        <v>10.10829312280777</v>
       </c>
       <c r="E98">
-        <v>4.8732</v>
+        <v>4.9599</v>
       </c>
       <c r="F98">
-        <v>8.3232</v>
+        <v>8.4099</v>
       </c>
       <c r="G98">
         <v>0.989</v>
@@ -9311,28 +9311,28 @@
         <v>1.440408163265306</v>
       </c>
       <c r="M98">
-        <v>0.63089856</v>
+        <v>0.6374704200000001</v>
       </c>
       <c r="N98">
-        <v>0.8095096032653061</v>
+        <v>0.802937743265306</v>
       </c>
       <c r="O98">
-        <v>0.2428528809795918</v>
+        <v>0.2408813229795918</v>
       </c>
       <c r="P98">
-        <v>0.5666567222857143</v>
+        <v>0.5620564202857142</v>
       </c>
       <c r="Q98">
-        <v>0.6466567222857144</v>
+        <v>0.6420564202857143</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>2.227949153822756</v>
+        <v>2.943072940187892</v>
       </c>
       <c r="T98">
-        <v>15.21490962113527</v>
+        <v>20.20106914117024</v>
       </c>
       <c r="U98">
         <v>0.07580000000000001</v>
@@ -9349,7 +9349,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>2.283105802722558</v>
+        <v>2.259568629498614</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9357,22 +9357,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.1397603882056369</v>
+        <v>0.1394652102583633</v>
       </c>
       <c r="C99">
-        <v>2.687393122807773</v>
+        <v>2.630372604904856</v>
       </c>
       <c r="D99">
-        <v>10.10829312280777</v>
+        <v>10.13797260490485</v>
       </c>
       <c r="E99">
-        <v>4.9599</v>
+        <v>5.046599999999999</v>
       </c>
       <c r="F99">
-        <v>8.4099</v>
+        <v>8.496599999999999</v>
       </c>
       <c r="G99">
         <v>0.989</v>
@@ -9393,28 +9393,28 @@
         <v>1.440408163265306</v>
       </c>
       <c r="M99">
-        <v>0.6374704200000001</v>
+        <v>0.64404228</v>
       </c>
       <c r="N99">
-        <v>0.802937743265306</v>
+        <v>0.7963658832653061</v>
       </c>
       <c r="O99">
-        <v>0.2408813229795918</v>
+        <v>0.2389097649795918</v>
       </c>
       <c r="P99">
-        <v>0.5620564202857142</v>
+        <v>0.5574561182857143</v>
       </c>
       <c r="Q99">
-        <v>0.6420564202857143</v>
+        <v>0.6374561182857144</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>2.943072940187892</v>
+        <v>4.373320512918163</v>
       </c>
       <c r="T99">
-        <v>20.20106914117024</v>
+        <v>30.17338818124018</v>
       </c>
       <c r="U99">
         <v>0.07580000000000001</v>
@@ -9431,7 +9431,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>2.259568629498614</v>
+        <v>2.236511806748629</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9439,22 +9439,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.1394652102583633</v>
+        <v>0.1391700323110898</v>
       </c>
       <c r="C100">
-        <v>2.630372604904856</v>
+        <v>2.573526887165718</v>
       </c>
       <c r="D100">
-        <v>10.13797260490485</v>
+        <v>10.16782688716572</v>
       </c>
       <c r="E100">
-        <v>5.046599999999999</v>
+        <v>5.133299999999999</v>
       </c>
       <c r="F100">
-        <v>8.496599999999999</v>
+        <v>8.583299999999999</v>
       </c>
       <c r="G100">
         <v>0.989</v>
@@ -9475,28 +9475,28 @@
         <v>1.440408163265306</v>
       </c>
       <c r="M100">
-        <v>0.64404228</v>
+        <v>0.6506141400000001</v>
       </c>
       <c r="N100">
-        <v>0.7963658832653061</v>
+        <v>0.789794023265306</v>
       </c>
       <c r="O100">
-        <v>0.2389097649795918</v>
+        <v>0.2369382069795918</v>
       </c>
       <c r="P100">
-        <v>0.5574561182857143</v>
+        <v>0.5528558162857142</v>
       </c>
       <c r="Q100">
-        <v>0.6374561182857144</v>
+        <v>0.6328558162857143</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>4.373320512918163</v>
+        <v>8.664063231108976</v>
       </c>
       <c r="T100">
-        <v>30.17338818124018</v>
+        <v>60.09034530144999</v>
       </c>
       <c r="U100">
         <v>0.07580000000000001</v>
@@ -9513,91 +9513,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>2.236511806748629</v>
+        <v>2.213920778397632</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.1391700323110898</v>
-      </c>
-      <c r="C101">
-        <v>2.573526887165718</v>
-      </c>
-      <c r="D101">
-        <v>10.16782688716572</v>
-      </c>
-      <c r="E101">
-        <v>5.133299999999999</v>
-      </c>
-      <c r="F101">
-        <v>8.583299999999999</v>
-      </c>
-      <c r="G101">
-        <v>0.989</v>
-      </c>
-      <c r="H101">
-        <v>5.22</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>1.520408163265306</v>
-      </c>
-      <c r="K101">
-        <v>0.08000000000000007</v>
-      </c>
-      <c r="L101">
-        <v>1.440408163265306</v>
-      </c>
-      <c r="M101">
-        <v>0.6506141400000001</v>
-      </c>
-      <c r="N101">
-        <v>0.789794023265306</v>
-      </c>
-      <c r="O101">
-        <v>0.2369382069795918</v>
-      </c>
-      <c r="P101">
-        <v>0.5528558162857142</v>
-      </c>
-      <c r="Q101">
-        <v>0.6328558162857143</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>8.664063231108976</v>
-      </c>
-      <c r="T101">
-        <v>60.09034530144999</v>
-      </c>
-      <c r="U101">
-        <v>0.07580000000000001</v>
-      </c>
-      <c r="V101">
-        <v>0.3</v>
-      </c>
-      <c r="W101">
-        <v>0.05306</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>B2/B</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>2.213920778397632</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
